--- a/meta analiz/Doruk_Reklam_Meta_Analiz.xlsx
+++ b/meta analiz/Doruk_Reklam_Meta_Analiz.xlsx
@@ -11,11 +11,13 @@
     <sheet name="2. Kategori Analizi" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="3. Kampanya Detayı" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="4. 60 Bin TL Dağıtımı" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Ham Veri (Kategorili)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="5. Sayfa x Amaç Matrisi" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6. Doktor Artış Senaryoları" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Ham Veri (Kategorili)" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Kampanya Detayı'!$A$1:$J$59</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ham Veri (Kategorili)'!$A$1:$K$763</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Ham Veri (Kategorili)'!$A$1:$K$763</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -28,7 +30,7 @@
     <numFmt numFmtId="165" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="28">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -165,8 +167,38 @@
       <color rgb="00777777"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000000FF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="006D4C7D"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="006D4C7D"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="006D4C7D"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -213,6 +245,16 @@
         <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006D4C7D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3EEF7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -240,7 +282,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -381,6 +423,49 @@
     <xf numFmtId="165" fontId="9" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="23" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" textRotation="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" textRotation="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" textRotation="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="21" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -4999,6 +5084,852 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="B2:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="24" t="inlineStr">
+        <is>
+          <t>SAYFA KATEGORİSİ × KAMPANYA AMACI MATRİSİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="53" t="inlineStr">
+        <is>
+          <t>Her sayfa kategorisinin altında amaçlar; tutar + oran + günlük 60.000 TL karşılığı. (Genel% = toplam içindeki pay, Sayfa-İçi% = o sayfanın kendi içindeki pay)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="57" t="inlineStr">
+        <is>
+          <t>Günlük Bütçe (TL) →</t>
+        </is>
+      </c>
+      <c r="D5" s="62" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="39" t="inlineStr">
+        <is>
+          <t>Sayfa Kategorisi</t>
+        </is>
+      </c>
+      <c r="C7" s="39" t="inlineStr">
+        <is>
+          <t>Amaç</t>
+        </is>
+      </c>
+      <c r="D7" s="39" t="inlineStr">
+        <is>
+          <t>Harcama 30g (TL)</t>
+        </is>
+      </c>
+      <c r="E7" s="39" t="inlineStr">
+        <is>
+          <t>Genel %</t>
+        </is>
+      </c>
+      <c r="F7" s="39" t="inlineStr">
+        <is>
+          <t>Sayfa-İçi %</t>
+        </is>
+      </c>
+      <c r="G7" s="39" t="inlineStr">
+        <is>
+          <t>Günlük (60K)</t>
+        </is>
+      </c>
+      <c r="H7" s="39" t="inlineStr">
+        <is>
+          <t>Aylık (60K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="63" t="inlineStr">
+        <is>
+          <t>Hastane (Kurumsal)</t>
+        </is>
+      </c>
+      <c r="C8" s="64" t="inlineStr">
+        <is>
+          <t>Lead Toplama (Form)</t>
+        </is>
+      </c>
+      <c r="D8" s="15">
+        <f>SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Hastane (Kurumsal)",'Ham Veri (Kategorili)'!$E$2:$E$763,"Lead Toplama (Form)")</f>
+        <v/>
+      </c>
+      <c r="E8" s="16">
+        <f>SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Hastane (Kurumsal)",'Ham Veri (Kategorili)'!$E$2:$E$763,"Lead Toplama (Form)")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763)</f>
+        <v/>
+      </c>
+      <c r="F8" s="65">
+        <f>SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Hastane (Kurumsal)",'Ham Veri (Kategorili)'!$E$2:$E$763,"Lead Toplama (Form)")/SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Hastane (Kurumsal)")</f>
+        <v/>
+      </c>
+      <c r="G8" s="66">
+        <f>(SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Hastane (Kurumsal)",'Ham Veri (Kategorili)'!$E$2:$E$763,"Lead Toplama (Form)")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763))*$D$5</f>
+        <v/>
+      </c>
+      <c r="H8" s="15">
+        <f>G8*30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="67" t="inlineStr"/>
+      <c r="C9" s="64" t="inlineStr">
+        <is>
+          <t>Instagram Öne Çıkarma</t>
+        </is>
+      </c>
+      <c r="D9" s="15">
+        <f>SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Hastane (Kurumsal)",'Ham Veri (Kategorili)'!$E$2:$E$763,"Instagram Öne Çıkarma")</f>
+        <v/>
+      </c>
+      <c r="E9" s="16">
+        <f>SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Hastane (Kurumsal)",'Ham Veri (Kategorili)'!$E$2:$E$763,"Instagram Öne Çıkarma")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763)</f>
+        <v/>
+      </c>
+      <c r="F9" s="65">
+        <f>SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Hastane (Kurumsal)",'Ham Veri (Kategorili)'!$E$2:$E$763,"Instagram Öne Çıkarma")/SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Hastane (Kurumsal)")</f>
+        <v/>
+      </c>
+      <c r="G9" s="66">
+        <f>(SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Hastane (Kurumsal)",'Ham Veri (Kategorili)'!$E$2:$E$763,"Instagram Öne Çıkarma")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763))*$D$5</f>
+        <v/>
+      </c>
+      <c r="H9" s="15">
+        <f>G9*30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="67" t="inlineStr"/>
+      <c r="C10" s="64" t="inlineStr">
+        <is>
+          <t>Marka Bilinirliği (Erişim)</t>
+        </is>
+      </c>
+      <c r="D10" s="15">
+        <f>SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Hastane (Kurumsal)",'Ham Veri (Kategorili)'!$E$2:$E$763,"Marka Bilinirliği (Erişim)")</f>
+        <v/>
+      </c>
+      <c r="E10" s="16">
+        <f>SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Hastane (Kurumsal)",'Ham Veri (Kategorili)'!$E$2:$E$763,"Marka Bilinirliği (Erişim)")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763)</f>
+        <v/>
+      </c>
+      <c r="F10" s="65">
+        <f>SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Hastane (Kurumsal)",'Ham Veri (Kategorili)'!$E$2:$E$763,"Marka Bilinirliği (Erişim)")/SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Hastane (Kurumsal)")</f>
+        <v/>
+      </c>
+      <c r="G10" s="66">
+        <f>(SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Hastane (Kurumsal)",'Ham Veri (Kategorili)'!$E$2:$E$763,"Marka Bilinirliği (Erişim)")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763))*$D$5</f>
+        <v/>
+      </c>
+      <c r="H10" s="15">
+        <f>G10*30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>— ALT TOPLAM</t>
+        </is>
+      </c>
+      <c r="D11" s="68">
+        <f>SUM(D8:D10)</f>
+        <v/>
+      </c>
+      <c r="E11" s="69">
+        <f>SUM(E8:E10)</f>
+        <v/>
+      </c>
+      <c r="F11" s="69">
+        <f>SUM(F8:F10)</f>
+        <v/>
+      </c>
+      <c r="G11" s="68">
+        <f>SUM(G8:G10)</f>
+        <v/>
+      </c>
+      <c r="H11" s="68">
+        <f>SUM(H8:H10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="70" t="inlineStr">
+        <is>
+          <t>Estetik Marka</t>
+        </is>
+      </c>
+      <c r="C12" s="64" t="inlineStr">
+        <is>
+          <t>Lead Toplama (Form)</t>
+        </is>
+      </c>
+      <c r="D12" s="15">
+        <f>SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Estetik Marka",'Ham Veri (Kategorili)'!$E$2:$E$763,"Lead Toplama (Form)")</f>
+        <v/>
+      </c>
+      <c r="E12" s="21">
+        <f>SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Estetik Marka",'Ham Veri (Kategorili)'!$E$2:$E$763,"Lead Toplama (Form)")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763)</f>
+        <v/>
+      </c>
+      <c r="F12" s="65">
+        <f>SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Estetik Marka",'Ham Veri (Kategorili)'!$E$2:$E$763,"Lead Toplama (Form)")/SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Estetik Marka")</f>
+        <v/>
+      </c>
+      <c r="G12" s="66">
+        <f>(SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Estetik Marka",'Ham Veri (Kategorili)'!$E$2:$E$763,"Lead Toplama (Form)")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763))*$D$5</f>
+        <v/>
+      </c>
+      <c r="H12" s="15">
+        <f>G12*30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="71" t="inlineStr"/>
+      <c r="C13" s="64" t="inlineStr">
+        <is>
+          <t>Instagram Öne Çıkarma</t>
+        </is>
+      </c>
+      <c r="D13" s="15">
+        <f>SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Estetik Marka",'Ham Veri (Kategorili)'!$E$2:$E$763,"Instagram Öne Çıkarma")</f>
+        <v/>
+      </c>
+      <c r="E13" s="21">
+        <f>SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Estetik Marka",'Ham Veri (Kategorili)'!$E$2:$E$763,"Instagram Öne Çıkarma")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763)</f>
+        <v/>
+      </c>
+      <c r="F13" s="65">
+        <f>SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Estetik Marka",'Ham Veri (Kategorili)'!$E$2:$E$763,"Instagram Öne Çıkarma")/SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Estetik Marka")</f>
+        <v/>
+      </c>
+      <c r="G13" s="66">
+        <f>(SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Estetik Marka",'Ham Veri (Kategorili)'!$E$2:$E$763,"Instagram Öne Çıkarma")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763))*$D$5</f>
+        <v/>
+      </c>
+      <c r="H13" s="15">
+        <f>G13*30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>— ALT TOPLAM</t>
+        </is>
+      </c>
+      <c r="D14" s="68">
+        <f>SUM(D12:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="69">
+        <f>SUM(E12:E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="69">
+        <f>SUM(F12:F13)</f>
+        <v/>
+      </c>
+      <c r="G14" s="68">
+        <f>SUM(G12:G13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="68">
+        <f>SUM(H12:H13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="72" t="inlineStr">
+        <is>
+          <t>Doktor Sayfaları</t>
+        </is>
+      </c>
+      <c r="C15" s="64" t="inlineStr">
+        <is>
+          <t>Instagram Öne Çıkarma</t>
+        </is>
+      </c>
+      <c r="D15" s="15">
+        <f>SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları",'Ham Veri (Kategorili)'!$E$2:$E$763,"Instagram Öne Çıkarma")</f>
+        <v/>
+      </c>
+      <c r="E15" s="73">
+        <f>SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları",'Ham Veri (Kategorili)'!$E$2:$E$763,"Instagram Öne Çıkarma")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763)</f>
+        <v/>
+      </c>
+      <c r="F15" s="65">
+        <f>SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları",'Ham Veri (Kategorili)'!$E$2:$E$763,"Instagram Öne Çıkarma")/SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları")</f>
+        <v/>
+      </c>
+      <c r="G15" s="66">
+        <f>(SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları",'Ham Veri (Kategorili)'!$E$2:$E$763,"Instagram Öne Çıkarma")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763))*$D$5</f>
+        <v/>
+      </c>
+      <c r="H15" s="15">
+        <f>G15*30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>— ALT TOPLAM</t>
+        </is>
+      </c>
+      <c r="D16" s="68">
+        <f>SUM(D15:D15)</f>
+        <v/>
+      </c>
+      <c r="E16" s="69">
+        <f>SUM(E15:E15)</f>
+        <v/>
+      </c>
+      <c r="F16" s="69">
+        <f>SUM(F15:F15)</f>
+        <v/>
+      </c>
+      <c r="G16" s="68">
+        <f>SUM(G15:G15)</f>
+        <v/>
+      </c>
+      <c r="H16" s="68">
+        <f>SUM(H15:H15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="32" t="inlineStr">
+        <is>
+          <t>GENEL TOPLAM</t>
+        </is>
+      </c>
+      <c r="C17" s="74" t="inlineStr"/>
+      <c r="D17" s="33">
+        <f>SUM('Ham Veri (Kategorili)'!$G$2:$G$763)</f>
+        <v/>
+      </c>
+      <c r="E17" s="34">
+        <f>SUM('Ham Veri (Kategorili)'!$G$2:$G$763)/SUM('Ham Veri (Kategorili)'!$G$2:$G$763)</f>
+        <v/>
+      </c>
+      <c r="F17" s="74" t="inlineStr"/>
+      <c r="G17" s="33">
+        <f>$D$5</f>
+        <v/>
+      </c>
+      <c r="H17" s="33">
+        <f>$D$5*30</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:E36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="24" t="inlineStr">
+        <is>
+          <t>GÜNLÜK 60.000 TL — DOKTOR ARTIŞ SENARYOLARI</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="53" t="inlineStr">
+        <is>
+          <t>Baz 60.000 TL dağılımı aynı oranlarda korunur; ek bütçe YALNIZCA doktor sayfalarına, üstüne eklenir. Diğer kalemler sabit kalır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="57" t="inlineStr">
+        <is>
+          <t>Baz Günlük Bütçe (TL) →</t>
+        </is>
+      </c>
+      <c r="C5" s="62" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="57" t="inlineStr">
+        <is>
+          <t>Senaryo 2 — Doktora Ek (TL) →</t>
+        </is>
+      </c>
+      <c r="C6" s="75" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="57" t="inlineStr">
+        <is>
+          <t>Senaryo 3 — Doktora Ek (TL) →</t>
+        </is>
+      </c>
+      <c r="C7" s="75" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>GÜNLÜK DAĞILIM (TL/gün)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Sayfa Kategorisi</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Senaryo 1 (Baz 60K)</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Senaryo 2 (+10K Doktor)</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Senaryo 3 (+20K Doktor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="64" t="inlineStr">
+        <is>
+          <t>Hastane (Kurumsal)</t>
+        </is>
+      </c>
+      <c r="C11" s="15">
+        <f>(SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Hastane (Kurumsal)")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763))*$C$5</f>
+        <v/>
+      </c>
+      <c r="D11" s="15">
+        <f>(SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Hastane (Kurumsal)")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763))*$C$5</f>
+        <v/>
+      </c>
+      <c r="E11" s="15">
+        <f>(SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Hastane (Kurumsal)")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763))*$C$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="64" t="inlineStr">
+        <is>
+          <t>Estetik Marka</t>
+        </is>
+      </c>
+      <c r="C12" s="15">
+        <f>(SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Estetik Marka")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763))*$C$5</f>
+        <v/>
+      </c>
+      <c r="D12" s="15">
+        <f>(SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Estetik Marka")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763))*$C$5</f>
+        <v/>
+      </c>
+      <c r="E12" s="15">
+        <f>(SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Estetik Marka")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763))*$C$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="76" t="inlineStr">
+        <is>
+          <t>Doktor Sayfaları</t>
+        </is>
+      </c>
+      <c r="C13" s="77">
+        <f>(SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763))*$C$5</f>
+        <v/>
+      </c>
+      <c r="D13" s="77">
+        <f>(SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763))*$C$5+$C$6</f>
+        <v/>
+      </c>
+      <c r="E13" s="77">
+        <f>(SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763))*$C$5+$C$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="32" t="inlineStr">
+        <is>
+          <t>GÜNLÜK TOPLAM</t>
+        </is>
+      </c>
+      <c r="C14" s="33">
+        <f>SUM(C11:C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="33">
+        <f>SUM(D11:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="33">
+        <f>SUM(E11:E13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="78" t="inlineStr">
+        <is>
+          <t>→ Doktor payı (% toplam)</t>
+        </is>
+      </c>
+      <c r="C15" s="79">
+        <f>C13/C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="79">
+        <f>D13/D14</f>
+        <v/>
+      </c>
+      <c r="E15" s="79">
+        <f>E13/E14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>AYLIK DAĞILIM (TL/ay = günlük × 30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>Sayfa Kategorisi</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>Senaryo 1 (Baz 60K)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>Senaryo 2 (+10K Doktor)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>Senaryo 3 (+20K Doktor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="64" t="inlineStr">
+        <is>
+          <t>Hastane (Kurumsal)</t>
+        </is>
+      </c>
+      <c r="C19" s="15">
+        <f>C11*30</f>
+        <v/>
+      </c>
+      <c r="D19" s="15">
+        <f>D11*30</f>
+        <v/>
+      </c>
+      <c r="E19" s="15">
+        <f>E11*30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="64" t="inlineStr">
+        <is>
+          <t>Estetik Marka</t>
+        </is>
+      </c>
+      <c r="C20" s="15">
+        <f>C12*30</f>
+        <v/>
+      </c>
+      <c r="D20" s="15">
+        <f>D12*30</f>
+        <v/>
+      </c>
+      <c r="E20" s="15">
+        <f>E12*30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="76" t="inlineStr">
+        <is>
+          <t>Doktor Sayfaları</t>
+        </is>
+      </c>
+      <c r="C21" s="77">
+        <f>C13*30</f>
+        <v/>
+      </c>
+      <c r="D21" s="77">
+        <f>D13*30</f>
+        <v/>
+      </c>
+      <c r="E21" s="77">
+        <f>E13*30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>AYLIK TOPLAM</t>
+        </is>
+      </c>
+      <c r="C22" s="33">
+        <f>SUM(C19:C21)</f>
+        <v/>
+      </c>
+      <c r="D22" s="33">
+        <f>SUM(D19:D21)</f>
+        <v/>
+      </c>
+      <c r="E22" s="33">
+        <f>SUM(E19:E21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="80" t="inlineStr">
+        <is>
+          <t>DOKTOR BAZINDA GÜNLÜK (ek, geçmiş paya göre 4 doktora bölünür)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="81" t="inlineStr">
+        <is>
+          <t>Doktor</t>
+        </is>
+      </c>
+      <c r="C25" s="81" t="inlineStr">
+        <is>
+          <t>Senaryo 1 (Baz)</t>
+        </is>
+      </c>
+      <c r="D25" s="81" t="inlineStr">
+        <is>
+          <t>Senaryo 2 (+10K)</t>
+        </is>
+      </c>
+      <c r="E25" s="81" t="inlineStr">
+        <is>
+          <t>Senaryo 3 (+20K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="64" t="inlineStr">
+        <is>
+          <t>Op.Dr. Abdullah ERTAŞ</t>
+        </is>
+      </c>
+      <c r="C26" s="15">
+        <f>(SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$A$2:$A$763,"Op.Dr. Abdullah ERTAŞ")/SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları"))*((SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763))*$C$5)</f>
+        <v/>
+      </c>
+      <c r="D26" s="15">
+        <f>(SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$A$2:$A$763,"Op.Dr. Abdullah ERTAŞ")/SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları"))*((SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763))*$C$5+$C$6)</f>
+        <v/>
+      </c>
+      <c r="E26" s="15">
+        <f>(SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$A$2:$A$763,"Op.Dr. Abdullah ERTAŞ")/SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları"))*((SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763))*$C$5+$C$7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="64" t="inlineStr">
+        <is>
+          <t>Op. Dr. Emre Çaycı</t>
+        </is>
+      </c>
+      <c r="C27" s="15">
+        <f>(SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$A$2:$A$763,"Op. Dr. Emre Çaycı")/SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları"))*((SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763))*$C$5)</f>
+        <v/>
+      </c>
+      <c r="D27" s="15">
+        <f>(SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$A$2:$A$763,"Op. Dr. Emre Çaycı")/SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları"))*((SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763))*$C$5+$C$6)</f>
+        <v/>
+      </c>
+      <c r="E27" s="15">
+        <f>(SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$A$2:$A$763,"Op. Dr. Emre Çaycı")/SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları"))*((SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763))*$C$5+$C$7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="64" t="inlineStr">
+        <is>
+          <t>Op.Dr. Eren Kaya</t>
+        </is>
+      </c>
+      <c r="C28" s="15">
+        <f>(SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$A$2:$A$763,"Op.Dr. Eren Kaya")/SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları"))*((SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763))*$C$5)</f>
+        <v/>
+      </c>
+      <c r="D28" s="15">
+        <f>(SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$A$2:$A$763,"Op.Dr. Eren Kaya")/SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları"))*((SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763))*$C$5+$C$6)</f>
+        <v/>
+      </c>
+      <c r="E28" s="15">
+        <f>(SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$A$2:$A$763,"Op.Dr. Eren Kaya")/SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları"))*((SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763))*$C$5+$C$7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="64" t="inlineStr">
+        <is>
+          <t>Doç.Dr. Selin Aktürk Esen</t>
+        </is>
+      </c>
+      <c r="C29" s="15">
+        <f>(SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$A$2:$A$763,"Doç.Dr. Selin Aktürk Esen")/SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları"))*((SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763))*$C$5)</f>
+        <v/>
+      </c>
+      <c r="D29" s="15">
+        <f>(SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$A$2:$A$763,"Doç.Dr. Selin Aktürk Esen")/SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları"))*((SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763))*$C$5+$C$6)</f>
+        <v/>
+      </c>
+      <c r="E29" s="15">
+        <f>(SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$A$2:$A$763,"Doç.Dr. Selin Aktürk Esen")/SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları"))*((SUMIFS('Ham Veri (Kategorili)'!$G$2:$G$763,'Ham Veri (Kategorili)'!$D$2:$D$763,"Doktor Sayfaları")/SUM('Ham Veri (Kategorili)'!$G$2:$G$763))*$C$5+$C$7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="32" t="inlineStr">
+        <is>
+          <t>DOKTOR TOPLAM</t>
+        </is>
+      </c>
+      <c r="C30" s="33">
+        <f>SUM(C26:C29)</f>
+        <v/>
+      </c>
+      <c r="D30" s="33">
+        <f>SUM(D26:D29)</f>
+        <v/>
+      </c>
+      <c r="E30" s="33">
+        <f>SUM(E26:E29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="82" t="inlineStr">
+        <is>
+          <t>Not: Senaryo 1 = 60.000 TL'nin geçmiş oranlarla dağılımı (doktor payı ≈ %6,2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="82" t="inlineStr">
+        <is>
+          <t>Senaryo 2 = Senaryo 1 + doktora ek 10.000 TL → günlük toplam 70.000 TL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="82" t="inlineStr">
+        <is>
+          <t>Senaryo 3 = Senaryo 1 + doktora ek 20.000 TL → günlük toplam 80.000 TL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="82" t="inlineStr">
+        <is>
+          <t>Hastane ve Estetik kalemleri üç senaryoda da sabittir; yalnızca doktor bütçesi artar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="82" t="inlineStr">
+        <is>
+          <t>Sarı hücreleri (baz bütçe / ek tutarlar) değiştirerek kendi senaryolarınızı üretebilirsiniz.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B32:E32"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K763"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5103,7 +6034,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G2" s="62" t="n">
+      <c r="G2" s="83" t="n">
         <v>1542.27</v>
       </c>
       <c r="H2" s="43" t="inlineStr">
@@ -5152,7 +6083,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G3" s="63" t="n">
+      <c r="G3" s="84" t="n">
         <v>1281.84</v>
       </c>
       <c r="H3" s="47" t="inlineStr">
@@ -5201,7 +6132,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G4" s="62" t="n">
+      <c r="G4" s="83" t="n">
         <v>1281.69</v>
       </c>
       <c r="H4" s="43" t="inlineStr">
@@ -5250,7 +6181,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G5" s="63" t="n">
+      <c r="G5" s="84" t="n">
         <v>1265.61</v>
       </c>
       <c r="H5" s="47" t="inlineStr">
@@ -5299,7 +6230,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G6" s="62" t="n">
+      <c r="G6" s="83" t="n">
         <v>1258.54</v>
       </c>
       <c r="H6" s="43" t="inlineStr">
@@ -5348,7 +6279,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G7" s="63" t="n">
+      <c r="G7" s="84" t="n">
         <v>1258.31</v>
       </c>
       <c r="H7" s="47" t="inlineStr">
@@ -5397,7 +6328,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G8" s="62" t="n">
+      <c r="G8" s="83" t="n">
         <v>1253.68</v>
       </c>
       <c r="H8" s="43" t="inlineStr">
@@ -5446,7 +6377,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G9" s="63" t="n">
+      <c r="G9" s="84" t="n">
         <v>1250.66</v>
       </c>
       <c r="H9" s="47" t="inlineStr">
@@ -5495,7 +6426,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G10" s="62" t="n">
+      <c r="G10" s="83" t="n">
         <v>1240.71</v>
       </c>
       <c r="H10" s="43" t="inlineStr">
@@ -5544,7 +6475,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G11" s="63" t="n">
+      <c r="G11" s="84" t="n">
         <v>1232.5</v>
       </c>
       <c r="H11" s="47" t="inlineStr">
@@ -5593,7 +6524,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G12" s="62" t="n">
+      <c r="G12" s="83" t="n">
         <v>1098.92</v>
       </c>
       <c r="H12" s="43" t="inlineStr">
@@ -5642,7 +6573,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G13" s="63" t="n">
+      <c r="G13" s="84" t="n">
         <v>1081.29</v>
       </c>
       <c r="H13" s="47" t="inlineStr">
@@ -5691,7 +6622,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G14" s="62" t="n">
+      <c r="G14" s="83" t="n">
         <v>1067.37</v>
       </c>
       <c r="H14" s="43" t="inlineStr">
@@ -5740,7 +6671,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G15" s="63" t="n">
+      <c r="G15" s="84" t="n">
         <v>1045.61</v>
       </c>
       <c r="H15" s="47" t="inlineStr">
@@ -5789,7 +6720,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G16" s="62" t="n">
+      <c r="G16" s="83" t="n">
         <v>1023.21</v>
       </c>
       <c r="H16" s="43" t="inlineStr">
@@ -5838,7 +6769,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G17" s="63" t="n">
+      <c r="G17" s="84" t="n">
         <v>1016.84</v>
       </c>
       <c r="H17" s="47" t="inlineStr">
@@ -5887,7 +6818,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G18" s="62" t="n">
+      <c r="G18" s="83" t="n">
         <v>1008.13</v>
       </c>
       <c r="H18" s="43" t="inlineStr">
@@ -5936,7 +6867,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G19" s="63" t="n">
+      <c r="G19" s="84" t="n">
         <v>1007.8</v>
       </c>
       <c r="H19" s="47" t="inlineStr">
@@ -5985,7 +6916,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G20" s="62" t="n">
+      <c r="G20" s="83" t="n">
         <v>999.9299999999999</v>
       </c>
       <c r="H20" s="43" t="inlineStr">
@@ -6034,7 +6965,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G21" s="63" t="n">
+      <c r="G21" s="84" t="n">
         <v>997.9</v>
       </c>
       <c r="H21" s="47" t="inlineStr">
@@ -6083,7 +7014,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G22" s="62" t="n">
+      <c r="G22" s="83" t="n">
         <v>990.72</v>
       </c>
       <c r="H22" s="43" t="inlineStr">
@@ -6132,7 +7063,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G23" s="63" t="n">
+      <c r="G23" s="84" t="n">
         <v>985.4</v>
       </c>
       <c r="H23" s="47" t="inlineStr">
@@ -6181,7 +7112,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G24" s="62" t="n">
+      <c r="G24" s="83" t="n">
         <v>982.49</v>
       </c>
       <c r="H24" s="43" t="inlineStr">
@@ -6230,7 +7161,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G25" s="63" t="n">
+      <c r="G25" s="84" t="n">
         <v>981.91</v>
       </c>
       <c r="H25" s="47" t="inlineStr">
@@ -6279,7 +7210,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G26" s="62" t="n">
+      <c r="G26" s="83" t="n">
         <v>974.65</v>
       </c>
       <c r="H26" s="43" t="inlineStr">
@@ -6328,7 +7259,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G27" s="63" t="n">
+      <c r="G27" s="84" t="n">
         <v>970.61</v>
       </c>
       <c r="H27" s="47" t="inlineStr">
@@ -6377,7 +7308,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G28" s="62" t="n">
+      <c r="G28" s="83" t="n">
         <v>966.46</v>
       </c>
       <c r="H28" s="43" t="inlineStr">
@@ -6426,7 +7357,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G29" s="63" t="n">
+      <c r="G29" s="84" t="n">
         <v>966.13</v>
       </c>
       <c r="H29" s="47" t="inlineStr">
@@ -6475,7 +7406,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G30" s="62" t="n">
+      <c r="G30" s="83" t="n">
         <v>962.33</v>
       </c>
       <c r="H30" s="43" t="inlineStr">
@@ -6524,7 +7455,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G31" s="63" t="n">
+      <c r="G31" s="84" t="n">
         <v>936.2</v>
       </c>
       <c r="H31" s="47" t="inlineStr">
@@ -6573,7 +7504,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G32" s="62" t="n">
+      <c r="G32" s="83" t="n">
         <v>935.28</v>
       </c>
       <c r="H32" s="43" t="inlineStr">
@@ -6622,7 +7553,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G33" s="63" t="n">
+      <c r="G33" s="84" t="n">
         <v>923.48</v>
       </c>
       <c r="H33" s="47" t="inlineStr">
@@ -6671,7 +7602,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G34" s="62" t="n">
+      <c r="G34" s="83" t="n">
         <v>921.85</v>
       </c>
       <c r="H34" s="43" t="inlineStr">
@@ -6720,7 +7651,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G35" s="63" t="n">
+      <c r="G35" s="84" t="n">
         <v>907.36</v>
       </c>
       <c r="H35" s="47" t="inlineStr">
@@ -6769,7 +7700,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G36" s="62" t="n">
+      <c r="G36" s="83" t="n">
         <v>891.63</v>
       </c>
       <c r="H36" s="43" t="inlineStr">
@@ -6818,7 +7749,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G37" s="63" t="n">
+      <c r="G37" s="84" t="n">
         <v>883.2</v>
       </c>
       <c r="H37" s="47" t="inlineStr">
@@ -6867,7 +7798,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G38" s="62" t="n">
+      <c r="G38" s="83" t="n">
         <v>875.4299999999999</v>
       </c>
       <c r="H38" s="43" t="inlineStr">
@@ -6916,7 +7847,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G39" s="63" t="n">
+      <c r="G39" s="84" t="n">
         <v>846.3</v>
       </c>
       <c r="H39" s="47" t="inlineStr">
@@ -6965,7 +7896,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G40" s="62" t="n">
+      <c r="G40" s="83" t="n">
         <v>844.29</v>
       </c>
       <c r="H40" s="43" t="inlineStr">
@@ -7014,7 +7945,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G41" s="63" t="n">
+      <c r="G41" s="84" t="n">
         <v>829.86</v>
       </c>
       <c r="H41" s="47" t="inlineStr">
@@ -7063,7 +7994,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G42" s="62" t="n">
+      <c r="G42" s="83" t="n">
         <v>825.95</v>
       </c>
       <c r="H42" s="43" t="inlineStr">
@@ -7112,7 +8043,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G43" s="63" t="n">
+      <c r="G43" s="84" t="n">
         <v>782.34</v>
       </c>
       <c r="H43" s="47" t="inlineStr">
@@ -7161,7 +8092,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G44" s="62" t="n">
+      <c r="G44" s="83" t="n">
         <v>769.12</v>
       </c>
       <c r="H44" s="43" t="inlineStr">
@@ -7210,7 +8141,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G45" s="63" t="n">
+      <c r="G45" s="84" t="n">
         <v>763.14</v>
       </c>
       <c r="H45" s="47" t="inlineStr">
@@ -7259,7 +8190,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G46" s="62" t="n">
+      <c r="G46" s="83" t="n">
         <v>758.59</v>
       </c>
       <c r="H46" s="43" t="inlineStr">
@@ -7308,7 +8239,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G47" s="63" t="n">
+      <c r="G47" s="84" t="n">
         <v>743.7</v>
       </c>
       <c r="H47" s="47" t="inlineStr">
@@ -7357,7 +8288,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G48" s="62" t="n">
+      <c r="G48" s="83" t="n">
         <v>736.09</v>
       </c>
       <c r="H48" s="43" t="inlineStr">
@@ -7406,7 +8337,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G49" s="63" t="n">
+      <c r="G49" s="84" t="n">
         <v>725.6799999999999</v>
       </c>
       <c r="H49" s="47" t="inlineStr">
@@ -7455,7 +8386,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G50" s="62" t="n">
+      <c r="G50" s="83" t="n">
         <v>707.21</v>
       </c>
       <c r="H50" s="43" t="inlineStr">
@@ -7504,7 +8435,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G51" s="63" t="n">
+      <c r="G51" s="84" t="n">
         <v>691.39</v>
       </c>
       <c r="H51" s="47" t="inlineStr">
@@ -7553,7 +8484,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G52" s="62" t="n">
+      <c r="G52" s="83" t="n">
         <v>680.98</v>
       </c>
       <c r="H52" s="43" t="inlineStr">
@@ -7602,7 +8533,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G53" s="63" t="n">
+      <c r="G53" s="84" t="n">
         <v>676.25</v>
       </c>
       <c r="H53" s="47" t="inlineStr">
@@ -7651,7 +8582,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G54" s="62" t="n">
+      <c r="G54" s="83" t="n">
         <v>672.5599999999999</v>
       </c>
       <c r="H54" s="43" t="inlineStr">
@@ -7700,7 +8631,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G55" s="63" t="n">
+      <c r="G55" s="84" t="n">
         <v>667.15</v>
       </c>
       <c r="H55" s="47" t="inlineStr">
@@ -7749,7 +8680,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G56" s="62" t="n">
+      <c r="G56" s="83" t="n">
         <v>660.08</v>
       </c>
       <c r="H56" s="43" t="inlineStr">
@@ -7798,7 +8729,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G57" s="63" t="n">
+      <c r="G57" s="84" t="n">
         <v>659.5</v>
       </c>
       <c r="H57" s="47" t="inlineStr">
@@ -7847,7 +8778,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G58" s="62" t="n">
+      <c r="G58" s="83" t="n">
         <v>652.37</v>
       </c>
       <c r="H58" s="43" t="inlineStr">
@@ -7896,7 +8827,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G59" s="63" t="n">
+      <c r="G59" s="84" t="n">
         <v>650.51</v>
       </c>
       <c r="H59" s="47" t="inlineStr">
@@ -7945,7 +8876,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G60" s="62" t="n">
+      <c r="G60" s="83" t="n">
         <v>641.24</v>
       </c>
       <c r="H60" s="43" t="inlineStr">
@@ -7994,7 +8925,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G61" s="63" t="n">
+      <c r="G61" s="84" t="n">
         <v>613.84</v>
       </c>
       <c r="H61" s="47" t="inlineStr">
@@ -8043,7 +8974,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G62" s="62" t="n">
+      <c r="G62" s="83" t="n">
         <v>605.53</v>
       </c>
       <c r="H62" s="43" t="inlineStr">
@@ -8092,7 +9023,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G63" s="63" t="n">
+      <c r="G63" s="84" t="n">
         <v>589.64</v>
       </c>
       <c r="H63" s="47" t="inlineStr">
@@ -8141,7 +9072,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G64" s="62" t="n">
+      <c r="G64" s="83" t="n">
         <v>564.58</v>
       </c>
       <c r="H64" s="43" t="inlineStr">
@@ -8190,7 +9121,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G65" s="63" t="n">
+      <c r="G65" s="84" t="n">
         <v>549.76</v>
       </c>
       <c r="H65" s="47" t="inlineStr">
@@ -8239,7 +9170,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G66" s="62" t="n">
+      <c r="G66" s="83" t="n">
         <v>468.78</v>
       </c>
       <c r="H66" s="43" t="inlineStr">
@@ -8288,7 +9219,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G67" s="63" t="n">
+      <c r="G67" s="84" t="n">
         <v>467.4</v>
       </c>
       <c r="H67" s="47" t="inlineStr">
@@ -8337,7 +9268,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G68" s="62" t="n">
+      <c r="G68" s="83" t="n">
         <v>426.68</v>
       </c>
       <c r="H68" s="43" t="inlineStr">
@@ -8386,7 +9317,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G69" s="63" t="n">
+      <c r="G69" s="84" t="n">
         <v>411.17</v>
       </c>
       <c r="H69" s="47" t="inlineStr">
@@ -8435,7 +9366,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G70" s="62" t="n">
+      <c r="G70" s="83" t="n">
         <v>407.16</v>
       </c>
       <c r="H70" s="43" t="inlineStr">
@@ -8484,7 +9415,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G71" s="63" t="n">
+      <c r="G71" s="84" t="n">
         <v>359.45</v>
       </c>
       <c r="H71" s="47" t="inlineStr">
@@ -8533,7 +9464,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G72" s="62" t="n">
+      <c r="G72" s="83" t="n">
         <v>350.58</v>
       </c>
       <c r="H72" s="43" t="inlineStr">
@@ -8582,7 +9513,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G73" s="63" t="n">
+      <c r="G73" s="84" t="n">
         <v>347.48</v>
       </c>
       <c r="H73" s="47" t="inlineStr">
@@ -8631,7 +9562,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G74" s="62" t="n">
+      <c r="G74" s="83" t="n">
         <v>339.41</v>
       </c>
       <c r="H74" s="43" t="inlineStr">
@@ -8680,7 +9611,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G75" s="63" t="n">
+      <c r="G75" s="84" t="n">
         <v>336.23</v>
       </c>
       <c r="H75" s="47" t="inlineStr">
@@ -8729,7 +9660,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G76" s="62" t="n">
+      <c r="G76" s="83" t="n">
         <v>303.78</v>
       </c>
       <c r="H76" s="43" t="inlineStr">
@@ -8778,7 +9709,7 @@
           <t>Öne Çıkarma - Doktor</t>
         </is>
       </c>
-      <c r="G77" s="63" t="n">
+      <c r="G77" s="84" t="n">
         <v>68.08</v>
       </c>
       <c r="H77" s="47" t="inlineStr">
@@ -8827,7 +9758,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G78" s="62" t="n">
+      <c r="G78" s="83" t="n">
         <v>861.3099999999999</v>
       </c>
       <c r="H78" s="43" t="inlineStr">
@@ -8876,7 +9807,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G79" s="63" t="n">
+      <c r="G79" s="84" t="n">
         <v>785.3</v>
       </c>
       <c r="H79" s="47" t="inlineStr">
@@ -8925,7 +9856,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G80" s="62" t="n">
+      <c r="G80" s="83" t="n">
         <v>780.14</v>
       </c>
       <c r="H80" s="43" t="inlineStr">
@@ -8974,7 +9905,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G81" s="63" t="n">
+      <c r="G81" s="84" t="n">
         <v>775.6799999999999</v>
       </c>
       <c r="H81" s="47" t="inlineStr">
@@ -9023,7 +9954,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G82" s="62" t="n">
+      <c r="G82" s="83" t="n">
         <v>770.24</v>
       </c>
       <c r="H82" s="43" t="inlineStr">
@@ -9072,7 +10003,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G83" s="63" t="n">
+      <c r="G83" s="84" t="n">
         <v>758.11</v>
       </c>
       <c r="H83" s="47" t="inlineStr">
@@ -9121,7 +10052,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G84" s="62" t="n">
+      <c r="G84" s="83" t="n">
         <v>685.88</v>
       </c>
       <c r="H84" s="43" t="inlineStr">
@@ -9170,7 +10101,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G85" s="63" t="n">
+      <c r="G85" s="84" t="n">
         <v>675.71</v>
       </c>
       <c r="H85" s="47" t="inlineStr">
@@ -9219,7 +10150,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G86" s="62" t="n">
+      <c r="G86" s="83" t="n">
         <v>668.4400000000001</v>
       </c>
       <c r="H86" s="43" t="inlineStr">
@@ -9268,7 +10199,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G87" s="63" t="n">
+      <c r="G87" s="84" t="n">
         <v>655.04</v>
       </c>
       <c r="H87" s="47" t="inlineStr">
@@ -9317,7 +10248,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G88" s="62" t="n">
+      <c r="G88" s="83" t="n">
         <v>643.6799999999999</v>
       </c>
       <c r="H88" s="43" t="inlineStr">
@@ -9366,7 +10297,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G89" s="63" t="n">
+      <c r="G89" s="84" t="n">
         <v>642.72</v>
       </c>
       <c r="H89" s="47" t="inlineStr">
@@ -9415,7 +10346,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G90" s="62" t="n">
+      <c r="G90" s="83" t="n">
         <v>633.71</v>
       </c>
       <c r="H90" s="43" t="inlineStr">
@@ -9464,7 +10395,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G91" s="63" t="n">
+      <c r="G91" s="84" t="n">
         <v>611.3</v>
       </c>
       <c r="H91" s="47" t="inlineStr">
@@ -9513,7 +10444,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G92" s="62" t="n">
+      <c r="G92" s="83" t="n">
         <v>604.27</v>
       </c>
       <c r="H92" s="43" t="inlineStr">
@@ -9562,7 +10493,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G93" s="63" t="n">
+      <c r="G93" s="84" t="n">
         <v>581.77</v>
       </c>
       <c r="H93" s="47" t="inlineStr">
@@ -9611,7 +10542,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G94" s="62" t="n">
+      <c r="G94" s="83" t="n">
         <v>570.3</v>
       </c>
       <c r="H94" s="43" t="inlineStr">
@@ -9660,7 +10591,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G95" s="63" t="n">
+      <c r="G95" s="84" t="n">
         <v>564.1</v>
       </c>
       <c r="H95" s="47" t="inlineStr">
@@ -9709,7 +10640,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G96" s="62" t="n">
+      <c r="G96" s="83" t="n">
         <v>562.1900000000001</v>
       </c>
       <c r="H96" s="43" t="inlineStr">
@@ -9758,7 +10689,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G97" s="63" t="n">
+      <c r="G97" s="84" t="n">
         <v>549.1</v>
       </c>
       <c r="H97" s="47" t="inlineStr">
@@ -9807,7 +10738,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G98" s="62" t="n">
+      <c r="G98" s="83" t="n">
         <v>540.74</v>
       </c>
       <c r="H98" s="43" t="inlineStr">
@@ -9856,7 +10787,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G99" s="63" t="n">
+      <c r="G99" s="84" t="n">
         <v>540.6</v>
       </c>
       <c r="H99" s="47" t="inlineStr">
@@ -9905,7 +10836,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G100" s="62" t="n">
+      <c r="G100" s="83" t="n">
         <v>533.6900000000001</v>
       </c>
       <c r="H100" s="43" t="inlineStr">
@@ -9954,7 +10885,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G101" s="63" t="n">
+      <c r="G101" s="84" t="n">
         <v>525.95</v>
       </c>
       <c r="H101" s="47" t="inlineStr">
@@ -10003,7 +10934,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G102" s="62" t="n">
+      <c r="G102" s="83" t="n">
         <v>524.15</v>
       </c>
       <c r="H102" s="43" t="inlineStr">
@@ -10052,7 +10983,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G103" s="63" t="n">
+      <c r="G103" s="84" t="n">
         <v>523.61</v>
       </c>
       <c r="H103" s="47" t="inlineStr">
@@ -10101,7 +11032,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G104" s="62" t="n">
+      <c r="G104" s="83" t="n">
         <v>518.64</v>
       </c>
       <c r="H104" s="43" t="inlineStr">
@@ -10150,7 +11081,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G105" s="63" t="n">
+      <c r="G105" s="84" t="n">
         <v>516.7</v>
       </c>
       <c r="H105" s="47" t="inlineStr">
@@ -10199,7 +11130,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G106" s="62" t="n">
+      <c r="G106" s="83" t="n">
         <v>516.08</v>
       </c>
       <c r="H106" s="43" t="inlineStr">
@@ -10248,7 +11179,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G107" s="63" t="n">
+      <c r="G107" s="84" t="n">
         <v>515.1900000000001</v>
       </c>
       <c r="H107" s="47" t="inlineStr">
@@ -10297,7 +11228,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G108" s="62" t="n">
+      <c r="G108" s="83" t="n">
         <v>512.61</v>
       </c>
       <c r="H108" s="43" t="inlineStr">
@@ -10346,7 +11277,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G109" s="63" t="n">
+      <c r="G109" s="84" t="n">
         <v>509.32</v>
       </c>
       <c r="H109" s="47" t="inlineStr">
@@ -10395,7 +11326,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G110" s="62" t="n">
+      <c r="G110" s="83" t="n">
         <v>506.18</v>
       </c>
       <c r="H110" s="43" t="inlineStr">
@@ -10444,7 +11375,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G111" s="63" t="n">
+      <c r="G111" s="84" t="n">
         <v>495.38</v>
       </c>
       <c r="H111" s="47" t="inlineStr">
@@ -10493,7 +11424,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G112" s="62" t="n">
+      <c r="G112" s="83" t="n">
         <v>494.61</v>
       </c>
       <c r="H112" s="43" t="inlineStr">
@@ -10542,7 +11473,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G113" s="63" t="n">
+      <c r="G113" s="84" t="n">
         <v>493.94</v>
       </c>
       <c r="H113" s="47" t="inlineStr">
@@ -10591,7 +11522,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G114" s="62" t="n">
+      <c r="G114" s="83" t="n">
         <v>492.61</v>
       </c>
       <c r="H114" s="43" t="inlineStr">
@@ -10640,7 +11571,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G115" s="63" t="n">
+      <c r="G115" s="84" t="n">
         <v>489.24</v>
       </c>
       <c r="H115" s="47" t="inlineStr">
@@ -10689,7 +11620,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G116" s="62" t="n">
+      <c r="G116" s="83" t="n">
         <v>477.84</v>
       </c>
       <c r="H116" s="43" t="inlineStr">
@@ -10738,7 +11669,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G117" s="63" t="n">
+      <c r="G117" s="84" t="n">
         <v>457.54</v>
       </c>
       <c r="H117" s="47" t="inlineStr">
@@ -10787,7 +11718,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G118" s="62" t="n">
+      <c r="G118" s="83" t="n">
         <v>446.37</v>
       </c>
       <c r="H118" s="43" t="inlineStr">
@@ -10836,7 +11767,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G119" s="63" t="n">
+      <c r="G119" s="84" t="n">
         <v>421.81</v>
       </c>
       <c r="H119" s="47" t="inlineStr">
@@ -10885,7 +11816,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G120" s="62" t="n">
+      <c r="G120" s="83" t="n">
         <v>418.88</v>
       </c>
       <c r="H120" s="43" t="inlineStr">
@@ -10934,7 +11865,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G121" s="63" t="n">
+      <c r="G121" s="84" t="n">
         <v>413.3</v>
       </c>
       <c r="H121" s="47" t="inlineStr">
@@ -10983,7 +11914,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G122" s="62" t="n">
+      <c r="G122" s="83" t="n">
         <v>397.66</v>
       </c>
       <c r="H122" s="43" t="inlineStr">
@@ -11032,7 +11963,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G123" s="63" t="n">
+      <c r="G123" s="84" t="n">
         <v>394.54</v>
       </c>
       <c r="H123" s="47" t="inlineStr">
@@ -11081,7 +12012,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G124" s="62" t="n">
+      <c r="G124" s="83" t="n">
         <v>384.69</v>
       </c>
       <c r="H124" s="43" t="inlineStr">
@@ -11130,7 +12061,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G125" s="63" t="n">
+      <c r="G125" s="84" t="n">
         <v>383.82</v>
       </c>
       <c r="H125" s="47" t="inlineStr">
@@ -11179,7 +12110,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G126" s="62" t="n">
+      <c r="G126" s="83" t="n">
         <v>382.26</v>
       </c>
       <c r="H126" s="43" t="inlineStr">
@@ -11228,7 +12159,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G127" s="63" t="n">
+      <c r="G127" s="84" t="n">
         <v>381.4</v>
       </c>
       <c r="H127" s="47" t="inlineStr">
@@ -11277,7 +12208,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G128" s="62" t="n">
+      <c r="G128" s="83" t="n">
         <v>378.24</v>
       </c>
       <c r="H128" s="43" t="inlineStr">
@@ -11326,7 +12257,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G129" s="63" t="n">
+      <c r="G129" s="84" t="n">
         <v>365.35</v>
       </c>
       <c r="H129" s="47" t="inlineStr">
@@ -11375,7 +12306,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G130" s="62" t="n">
+      <c r="G130" s="83" t="n">
         <v>364.22</v>
       </c>
       <c r="H130" s="43" t="inlineStr">
@@ -11424,7 +12355,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G131" s="63" t="n">
+      <c r="G131" s="84" t="n">
         <v>362.68</v>
       </c>
       <c r="H131" s="47" t="inlineStr">
@@ -11473,7 +12404,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G132" s="62" t="n">
+      <c r="G132" s="83" t="n">
         <v>359.56</v>
       </c>
       <c r="H132" s="43" t="inlineStr">
@@ -11522,7 +12453,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G133" s="63" t="n">
+      <c r="G133" s="84" t="n">
         <v>311.14</v>
       </c>
       <c r="H133" s="47" t="inlineStr">
@@ -11571,7 +12502,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G134" s="62" t="n">
+      <c r="G134" s="83" t="n">
         <v>308.22</v>
       </c>
       <c r="H134" s="43" t="inlineStr">
@@ -11620,7 +12551,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G135" s="63" t="n">
+      <c r="G135" s="84" t="n">
         <v>307.62</v>
       </c>
       <c r="H135" s="47" t="inlineStr">
@@ -11669,7 +12600,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G136" s="62" t="n">
+      <c r="G136" s="83" t="n">
         <v>302.73</v>
       </c>
       <c r="H136" s="43" t="inlineStr">
@@ -11718,7 +12649,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G137" s="63" t="n">
+      <c r="G137" s="84" t="n">
         <v>283.77</v>
       </c>
       <c r="H137" s="47" t="inlineStr">
@@ -11767,7 +12698,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G138" s="62" t="n">
+      <c r="G138" s="83" t="n">
         <v>279.36</v>
       </c>
       <c r="H138" s="43" t="inlineStr">
@@ -11816,7 +12747,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G139" s="63" t="n">
+      <c r="G139" s="84" t="n">
         <v>277.75</v>
       </c>
       <c r="H139" s="47" t="inlineStr">
@@ -11865,7 +12796,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G140" s="62" t="n">
+      <c r="G140" s="83" t="n">
         <v>276.52</v>
       </c>
       <c r="H140" s="43" t="inlineStr">
@@ -11914,7 +12845,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G141" s="63" t="n">
+      <c r="G141" s="84" t="n">
         <v>264.68</v>
       </c>
       <c r="H141" s="47" t="inlineStr">
@@ -11963,7 +12894,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G142" s="62" t="n">
+      <c r="G142" s="83" t="n">
         <v>233.59</v>
       </c>
       <c r="H142" s="43" t="inlineStr">
@@ -12012,7 +12943,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G143" s="63" t="n">
+      <c r="G143" s="84" t="n">
         <v>221.94</v>
       </c>
       <c r="H143" s="47" t="inlineStr">
@@ -12061,7 +12992,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G144" s="62" t="n">
+      <c r="G144" s="83" t="n">
         <v>169.06</v>
       </c>
       <c r="H144" s="43" t="inlineStr">
@@ -12110,7 +13041,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G145" s="63" t="n">
+      <c r="G145" s="84" t="n">
         <v>168.97</v>
       </c>
       <c r="H145" s="47" t="inlineStr">
@@ -12159,7 +13090,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G146" s="62" t="n">
+      <c r="G146" s="83" t="n">
         <v>162.79</v>
       </c>
       <c r="H146" s="43" t="inlineStr">
@@ -12208,7 +13139,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G147" s="63" t="n">
+      <c r="G147" s="84" t="n">
         <v>161.43</v>
       </c>
       <c r="H147" s="47" t="inlineStr">
@@ -12257,7 +13188,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G148" s="62" t="n">
+      <c r="G148" s="83" t="n">
         <v>152.48</v>
       </c>
       <c r="H148" s="43" t="inlineStr">
@@ -12306,7 +13237,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G149" s="63" t="n">
+      <c r="G149" s="84" t="n">
         <v>151.72</v>
       </c>
       <c r="H149" s="47" t="inlineStr">
@@ -12355,7 +13286,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G150" s="62" t="n">
+      <c r="G150" s="83" t="n">
         <v>144.23</v>
       </c>
       <c r="H150" s="43" t="inlineStr">
@@ -12404,7 +13335,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G151" s="63" t="n">
+      <c r="G151" s="84" t="n">
         <v>138.83</v>
       </c>
       <c r="H151" s="47" t="inlineStr">
@@ -12453,7 +13384,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G152" s="62" t="n">
+      <c r="G152" s="83" t="n">
         <v>133.37</v>
       </c>
       <c r="H152" s="43" t="inlineStr">
@@ -12502,7 +13433,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G153" s="63" t="n">
+      <c r="G153" s="84" t="n">
         <v>119.9</v>
       </c>
       <c r="H153" s="47" t="inlineStr">
@@ -12551,7 +13482,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G154" s="62" t="n">
+      <c r="G154" s="83" t="n">
         <v>92.7</v>
       </c>
       <c r="H154" s="43" t="inlineStr">
@@ -12600,7 +13531,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G155" s="63" t="n">
+      <c r="G155" s="84" t="n">
         <v>80.7</v>
       </c>
       <c r="H155" s="47" t="inlineStr">
@@ -12649,7 +13580,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G156" s="62" t="n">
+      <c r="G156" s="83" t="n">
         <v>72.89</v>
       </c>
       <c r="H156" s="43" t="inlineStr">
@@ -12698,7 +13629,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G157" s="63" t="n">
+      <c r="G157" s="84" t="n">
         <v>63.97</v>
       </c>
       <c r="H157" s="47" t="inlineStr">
@@ -12747,7 +13678,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G158" s="62" t="n">
+      <c r="G158" s="83" t="n">
         <v>59.88</v>
       </c>
       <c r="H158" s="43" t="inlineStr">
@@ -12796,7 +13727,7 @@
           <t>Öne Çıkarma - Doruk Estetik</t>
         </is>
       </c>
-      <c r="G159" s="63" t="n">
+      <c r="G159" s="84" t="n">
         <v>52.13</v>
       </c>
       <c r="H159" s="47" t="inlineStr">
@@ -12845,7 +13776,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G160" s="62" t="n">
+      <c r="G160" s="83" t="n">
         <v>4145.8</v>
       </c>
       <c r="H160" s="43" t="inlineStr">
@@ -12894,7 +13825,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G161" s="63" t="n">
+      <c r="G161" s="84" t="n">
         <v>4001.26</v>
       </c>
       <c r="H161" s="47" t="inlineStr">
@@ -12943,7 +13874,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G162" s="62" t="n">
+      <c r="G162" s="83" t="n">
         <v>3406.22</v>
       </c>
       <c r="H162" s="43" t="inlineStr">
@@ -12992,7 +13923,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G163" s="63" t="n">
+      <c r="G163" s="84" t="n">
         <v>3399.56</v>
       </c>
       <c r="H163" s="47" t="inlineStr">
@@ -13041,7 +13972,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G164" s="62" t="n">
+      <c r="G164" s="83" t="n">
         <v>3175.63</v>
       </c>
       <c r="H164" s="43" t="inlineStr">
@@ -13090,7 +14021,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G165" s="63" t="n">
+      <c r="G165" s="84" t="n">
         <v>3160.36</v>
       </c>
       <c r="H165" s="47" t="inlineStr">
@@ -13139,7 +14070,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G166" s="62" t="n">
+      <c r="G166" s="83" t="n">
         <v>2834.24</v>
       </c>
       <c r="H166" s="43" t="inlineStr">
@@ -13188,7 +14119,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G167" s="63" t="n">
+      <c r="G167" s="84" t="n">
         <v>2774.88</v>
       </c>
       <c r="H167" s="47" t="inlineStr">
@@ -13237,7 +14168,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G168" s="62" t="n">
+      <c r="G168" s="83" t="n">
         <v>2759.89</v>
       </c>
       <c r="H168" s="43" t="inlineStr">
@@ -13286,7 +14217,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G169" s="63" t="n">
+      <c r="G169" s="84" t="n">
         <v>2705.98</v>
       </c>
       <c r="H169" s="47" t="inlineStr">
@@ -13335,7 +14266,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G170" s="62" t="n">
+      <c r="G170" s="83" t="n">
         <v>2666.55</v>
       </c>
       <c r="H170" s="43" t="inlineStr">
@@ -13384,7 +14315,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G171" s="63" t="n">
+      <c r="G171" s="84" t="n">
         <v>2574.58</v>
       </c>
       <c r="H171" s="47" t="inlineStr">
@@ -13433,7 +14364,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G172" s="62" t="n">
+      <c r="G172" s="83" t="n">
         <v>2480.41</v>
       </c>
       <c r="H172" s="43" t="inlineStr">
@@ -13482,7 +14413,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G173" s="63" t="n">
+      <c r="G173" s="84" t="n">
         <v>2388.1</v>
       </c>
       <c r="H173" s="47" t="inlineStr">
@@ -13531,7 +14462,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G174" s="62" t="n">
+      <c r="G174" s="83" t="n">
         <v>2364.73</v>
       </c>
       <c r="H174" s="43" t="inlineStr">
@@ -13580,7 +14511,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G175" s="63" t="n">
+      <c r="G175" s="84" t="n">
         <v>2188.94</v>
       </c>
       <c r="H175" s="47" t="inlineStr">
@@ -13629,7 +14560,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G176" s="62" t="n">
+      <c r="G176" s="83" t="n">
         <v>2043.81</v>
       </c>
       <c r="H176" s="43" t="inlineStr">
@@ -13678,7 +14609,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G177" s="63" t="n">
+      <c r="G177" s="84" t="n">
         <v>1950.24</v>
       </c>
       <c r="H177" s="47" t="inlineStr">
@@ -13727,7 +14658,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G178" s="62" t="n">
+      <c r="G178" s="83" t="n">
         <v>1915.96</v>
       </c>
       <c r="H178" s="43" t="inlineStr">
@@ -13776,7 +14707,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G179" s="63" t="n">
+      <c r="G179" s="84" t="n">
         <v>1752.65</v>
       </c>
       <c r="H179" s="47" t="inlineStr">
@@ -13825,7 +14756,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G180" s="62" t="n">
+      <c r="G180" s="83" t="n">
         <v>1513.14</v>
       </c>
       <c r="H180" s="43" t="inlineStr">
@@ -13874,7 +14805,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G181" s="63" t="n">
+      <c r="G181" s="84" t="n">
         <v>1395.12</v>
       </c>
       <c r="H181" s="47" t="inlineStr">
@@ -13923,7 +14854,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G182" s="62" t="n">
+      <c r="G182" s="83" t="n">
         <v>781.6</v>
       </c>
       <c r="H182" s="43" t="inlineStr">
@@ -13972,7 +14903,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G183" s="63" t="n">
+      <c r="G183" s="84" t="n">
         <v>745.41</v>
       </c>
       <c r="H183" s="47" t="inlineStr">
@@ -14021,7 +14952,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G184" s="62" t="n">
+      <c r="G184" s="83" t="n">
         <v>589.04</v>
       </c>
       <c r="H184" s="43" t="inlineStr">
@@ -14070,7 +15001,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G185" s="63" t="n">
+      <c r="G185" s="84" t="n">
         <v>379.16</v>
       </c>
       <c r="H185" s="47" t="inlineStr">
@@ -14119,7 +15050,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G186" s="62" t="n">
+      <c r="G186" s="83" t="n">
         <v>6851.98</v>
       </c>
       <c r="H186" s="43" t="inlineStr">
@@ -14168,7 +15099,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G187" s="63" t="n">
+      <c r="G187" s="84" t="n">
         <v>6367.51</v>
       </c>
       <c r="H187" s="47" t="inlineStr">
@@ -14217,7 +15148,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G188" s="62" t="n">
+      <c r="G188" s="83" t="n">
         <v>5617.01</v>
       </c>
       <c r="H188" s="43" t="inlineStr">
@@ -14266,7 +15197,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G189" s="63" t="n">
+      <c r="G189" s="84" t="n">
         <v>5277.94</v>
       </c>
       <c r="H189" s="47" t="inlineStr">
@@ -14315,7 +15246,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G190" s="62" t="n">
+      <c r="G190" s="83" t="n">
         <v>5256.93</v>
       </c>
       <c r="H190" s="43" t="inlineStr">
@@ -14364,7 +15295,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G191" s="63" t="n">
+      <c r="G191" s="84" t="n">
         <v>4703.02</v>
       </c>
       <c r="H191" s="47" t="inlineStr">
@@ -14413,7 +15344,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G192" s="62" t="n">
+      <c r="G192" s="83" t="n">
         <v>4680.76</v>
       </c>
       <c r="H192" s="43" t="inlineStr">
@@ -14462,7 +15393,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G193" s="63" t="n">
+      <c r="G193" s="84" t="n">
         <v>4599.17</v>
       </c>
       <c r="H193" s="47" t="inlineStr">
@@ -14511,7 +15442,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G194" s="62" t="n">
+      <c r="G194" s="83" t="n">
         <v>4544.02</v>
       </c>
       <c r="H194" s="43" t="inlineStr">
@@ -14560,7 +15491,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G195" s="63" t="n">
+      <c r="G195" s="84" t="n">
         <v>4360.37</v>
       </c>
       <c r="H195" s="47" t="inlineStr">
@@ -14609,7 +15540,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G196" s="62" t="n">
+      <c r="G196" s="83" t="n">
         <v>4328.79</v>
       </c>
       <c r="H196" s="43" t="inlineStr">
@@ -14658,7 +15589,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G197" s="63" t="n">
+      <c r="G197" s="84" t="n">
         <v>4242.28</v>
       </c>
       <c r="H197" s="47" t="inlineStr">
@@ -14707,7 +15638,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G198" s="62" t="n">
+      <c r="G198" s="83" t="n">
         <v>4039.18</v>
       </c>
       <c r="H198" s="43" t="inlineStr">
@@ -14756,7 +15687,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G199" s="63" t="n">
+      <c r="G199" s="84" t="n">
         <v>3923.96</v>
       </c>
       <c r="H199" s="47" t="inlineStr">
@@ -14805,7 +15736,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G200" s="62" t="n">
+      <c r="G200" s="83" t="n">
         <v>3714.23</v>
       </c>
       <c r="H200" s="43" t="inlineStr">
@@ -14854,7 +15785,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G201" s="63" t="n">
+      <c r="G201" s="84" t="n">
         <v>3652.58</v>
       </c>
       <c r="H201" s="47" t="inlineStr">
@@ -14903,7 +15834,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G202" s="62" t="n">
+      <c r="G202" s="83" t="n">
         <v>3542.02</v>
       </c>
       <c r="H202" s="43" t="inlineStr">
@@ -14952,7 +15883,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G203" s="63" t="n">
+      <c r="G203" s="84" t="n">
         <v>3451.9</v>
       </c>
       <c r="H203" s="47" t="inlineStr">
@@ -15001,7 +15932,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G204" s="62" t="n">
+      <c r="G204" s="83" t="n">
         <v>3372.85</v>
       </c>
       <c r="H204" s="43" t="inlineStr">
@@ -15050,7 +15981,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G205" s="63" t="n">
+      <c r="G205" s="84" t="n">
         <v>3337.8</v>
       </c>
       <c r="H205" s="47" t="inlineStr">
@@ -15099,7 +16030,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G206" s="62" t="n">
+      <c r="G206" s="83" t="n">
         <v>3192.47</v>
       </c>
       <c r="H206" s="43" t="inlineStr">
@@ -15148,7 +16079,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G207" s="63" t="n">
+      <c r="G207" s="84" t="n">
         <v>3073.8</v>
       </c>
       <c r="H207" s="47" t="inlineStr">
@@ -15197,7 +16128,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G208" s="62" t="n">
+      <c r="G208" s="83" t="n">
         <v>3012.72</v>
       </c>
       <c r="H208" s="43" t="inlineStr">
@@ -15246,7 +16177,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G209" s="63" t="n">
+      <c r="G209" s="84" t="n">
         <v>2973.97</v>
       </c>
       <c r="H209" s="47" t="inlineStr">
@@ -15295,7 +16226,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G210" s="62" t="n">
+      <c r="G210" s="83" t="n">
         <v>2896.72</v>
       </c>
       <c r="H210" s="43" t="inlineStr">
@@ -15344,7 +16275,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G211" s="63" t="n">
+      <c r="G211" s="84" t="n">
         <v>2810.28</v>
       </c>
       <c r="H211" s="47" t="inlineStr">
@@ -15393,7 +16324,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G212" s="62" t="n">
+      <c r="G212" s="83" t="n">
         <v>2750.84</v>
       </c>
       <c r="H212" s="43" t="inlineStr">
@@ -15442,7 +16373,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G213" s="63" t="n">
+      <c r="G213" s="84" t="n">
         <v>2736.43</v>
       </c>
       <c r="H213" s="47" t="inlineStr">
@@ -15491,7 +16422,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G214" s="62" t="n">
+      <c r="G214" s="83" t="n">
         <v>2663.78</v>
       </c>
       <c r="H214" s="43" t="inlineStr">
@@ -15540,7 +16471,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G215" s="63" t="n">
+      <c r="G215" s="84" t="n">
         <v>2455.02</v>
       </c>
       <c r="H215" s="47" t="inlineStr">
@@ -15589,7 +16520,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G216" s="62" t="n">
+      <c r="G216" s="83" t="n">
         <v>2374.15</v>
       </c>
       <c r="H216" s="43" t="inlineStr">
@@ -15638,7 +16569,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G217" s="63" t="n">
+      <c r="G217" s="84" t="n">
         <v>2298.04</v>
       </c>
       <c r="H217" s="47" t="inlineStr">
@@ -15687,7 +16618,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G218" s="62" t="n">
+      <c r="G218" s="83" t="n">
         <v>2263.35</v>
       </c>
       <c r="H218" s="43" t="inlineStr">
@@ -15736,7 +16667,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G219" s="63" t="n">
+      <c r="G219" s="84" t="n">
         <v>2220.32</v>
       </c>
       <c r="H219" s="47" t="inlineStr">
@@ -15785,7 +16716,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G220" s="62" t="n">
+      <c r="G220" s="83" t="n">
         <v>2148.93</v>
       </c>
       <c r="H220" s="43" t="inlineStr">
@@ -15834,7 +16765,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G221" s="63" t="n">
+      <c r="G221" s="84" t="n">
         <v>1997.1</v>
       </c>
       <c r="H221" s="47" t="inlineStr">
@@ -15883,7 +16814,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G222" s="62" t="n">
+      <c r="G222" s="83" t="n">
         <v>1676.78</v>
       </c>
       <c r="H222" s="43" t="inlineStr">
@@ -15932,7 +16863,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G223" s="63" t="n">
+      <c r="G223" s="84" t="n">
         <v>1267.72</v>
       </c>
       <c r="H223" s="47" t="inlineStr">
@@ -15981,7 +16912,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G224" s="62" t="n">
+      <c r="G224" s="83" t="n">
         <v>1264.45</v>
       </c>
       <c r="H224" s="43" t="inlineStr">
@@ -16030,7 +16961,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G225" s="63" t="n">
+      <c r="G225" s="84" t="n">
         <v>1178.48</v>
       </c>
       <c r="H225" s="47" t="inlineStr">
@@ -16079,7 +17010,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G226" s="62" t="n">
+      <c r="G226" s="83" t="n">
         <v>1149.79</v>
       </c>
       <c r="H226" s="43" t="inlineStr">
@@ -16128,7 +17059,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G227" s="63" t="n">
+      <c r="G227" s="84" t="n">
         <v>1079.97</v>
       </c>
       <c r="H227" s="47" t="inlineStr">
@@ -16177,7 +17108,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G228" s="62" t="n">
+      <c r="G228" s="83" t="n">
         <v>1046.22</v>
       </c>
       <c r="H228" s="43" t="inlineStr">
@@ -16226,7 +17157,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G229" s="63" t="n">
+      <c r="G229" s="84" t="n">
         <v>1045.75</v>
       </c>
       <c r="H229" s="47" t="inlineStr">
@@ -16275,7 +17206,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G230" s="62" t="n">
+      <c r="G230" s="83" t="n">
         <v>1043.96</v>
       </c>
       <c r="H230" s="43" t="inlineStr">
@@ -16324,7 +17255,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G231" s="63" t="n">
+      <c r="G231" s="84" t="n">
         <v>1040.02</v>
       </c>
       <c r="H231" s="47" t="inlineStr">
@@ -16373,7 +17304,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G232" s="62" t="n">
+      <c r="G232" s="83" t="n">
         <v>1017.89</v>
       </c>
       <c r="H232" s="43" t="inlineStr">
@@ -16422,7 +17353,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G233" s="63" t="n">
+      <c r="G233" s="84" t="n">
         <v>1012.76</v>
       </c>
       <c r="H233" s="47" t="inlineStr">
@@ -16471,7 +17402,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G234" s="62" t="n">
+      <c r="G234" s="83" t="n">
         <v>997.11</v>
       </c>
       <c r="H234" s="43" t="inlineStr">
@@ -16520,7 +17451,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G235" s="63" t="n">
+      <c r="G235" s="84" t="n">
         <v>995.25</v>
       </c>
       <c r="H235" s="47" t="inlineStr">
@@ -16569,7 +17500,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G236" s="62" t="n">
+      <c r="G236" s="83" t="n">
         <v>992.01</v>
       </c>
       <c r="H236" s="43" t="inlineStr">
@@ -16618,7 +17549,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G237" s="63" t="n">
+      <c r="G237" s="84" t="n">
         <v>980.77</v>
       </c>
       <c r="H237" s="47" t="inlineStr">
@@ -16667,7 +17598,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G238" s="62" t="n">
+      <c r="G238" s="83" t="n">
         <v>964.03</v>
       </c>
       <c r="H238" s="43" t="inlineStr">
@@ -16716,7 +17647,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G239" s="63" t="n">
+      <c r="G239" s="84" t="n">
         <v>959.49</v>
       </c>
       <c r="H239" s="47" t="inlineStr">
@@ -16765,7 +17696,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G240" s="62" t="n">
+      <c r="G240" s="83" t="n">
         <v>948.13</v>
       </c>
       <c r="H240" s="43" t="inlineStr">
@@ -16814,7 +17745,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G241" s="63" t="n">
+      <c r="G241" s="84" t="n">
         <v>947.76</v>
       </c>
       <c r="H241" s="47" t="inlineStr">
@@ -16863,7 +17794,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G242" s="62" t="n">
+      <c r="G242" s="83" t="n">
         <v>938.53</v>
       </c>
       <c r="H242" s="43" t="inlineStr">
@@ -16912,7 +17843,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G243" s="63" t="n">
+      <c r="G243" s="84" t="n">
         <v>923.66</v>
       </c>
       <c r="H243" s="47" t="inlineStr">
@@ -16961,7 +17892,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G244" s="62" t="n">
+      <c r="G244" s="83" t="n">
         <v>909.9</v>
       </c>
       <c r="H244" s="43" t="inlineStr">
@@ -17010,7 +17941,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G245" s="63" t="n">
+      <c r="G245" s="84" t="n">
         <v>907.58</v>
       </c>
       <c r="H245" s="47" t="inlineStr">
@@ -17059,7 +17990,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G246" s="62" t="n">
+      <c r="G246" s="83" t="n">
         <v>907.48</v>
       </c>
       <c r="H246" s="43" t="inlineStr">
@@ -17108,7 +18039,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G247" s="63" t="n">
+      <c r="G247" s="84" t="n">
         <v>904.23</v>
       </c>
       <c r="H247" s="47" t="inlineStr">
@@ -17157,7 +18088,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G248" s="62" t="n">
+      <c r="G248" s="83" t="n">
         <v>878.4299999999999</v>
       </c>
       <c r="H248" s="43" t="inlineStr">
@@ -17206,7 +18137,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G249" s="63" t="n">
+      <c r="G249" s="84" t="n">
         <v>852.38</v>
       </c>
       <c r="H249" s="47" t="inlineStr">
@@ -17255,7 +18186,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G250" s="62" t="n">
+      <c r="G250" s="83" t="n">
         <v>842.24</v>
       </c>
       <c r="H250" s="43" t="inlineStr">
@@ -17304,7 +18235,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G251" s="63" t="n">
+      <c r="G251" s="84" t="n">
         <v>820.58</v>
       </c>
       <c r="H251" s="47" t="inlineStr">
@@ -17353,7 +18284,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G252" s="62" t="n">
+      <c r="G252" s="83" t="n">
         <v>817.73</v>
       </c>
       <c r="H252" s="43" t="inlineStr">
@@ -17402,7 +18333,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G253" s="63" t="n">
+      <c r="G253" s="84" t="n">
         <v>814.1900000000001</v>
       </c>
       <c r="H253" s="47" t="inlineStr">
@@ -17451,7 +18382,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G254" s="62" t="n">
+      <c r="G254" s="83" t="n">
         <v>766.84</v>
       </c>
       <c r="H254" s="43" t="inlineStr">
@@ -17500,7 +18431,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G255" s="63" t="n">
+      <c r="G255" s="84" t="n">
         <v>755.03</v>
       </c>
       <c r="H255" s="47" t="inlineStr">
@@ -17549,7 +18480,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G256" s="62" t="n">
+      <c r="G256" s="83" t="n">
         <v>727.36</v>
       </c>
       <c r="H256" s="43" t="inlineStr">
@@ -17598,7 +18529,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G257" s="63" t="n">
+      <c r="G257" s="84" t="n">
         <v>703.16</v>
       </c>
       <c r="H257" s="47" t="inlineStr">
@@ -17647,7 +18578,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G258" s="62" t="n">
+      <c r="G258" s="83" t="n">
         <v>697.63</v>
       </c>
       <c r="H258" s="43" t="inlineStr">
@@ -17696,7 +18627,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G259" s="63" t="n">
+      <c r="G259" s="84" t="n">
         <v>696.26</v>
       </c>
       <c r="H259" s="47" t="inlineStr">
@@ -17745,7 +18676,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G260" s="62" t="n">
+      <c r="G260" s="83" t="n">
         <v>645.35</v>
       </c>
       <c r="H260" s="43" t="inlineStr">
@@ -17794,7 +18725,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G261" s="63" t="n">
+      <c r="G261" s="84" t="n">
         <v>605.9</v>
       </c>
       <c r="H261" s="47" t="inlineStr">
@@ -17843,7 +18774,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G262" s="62" t="n">
+      <c r="G262" s="83" t="n">
         <v>587.05</v>
       </c>
       <c r="H262" s="43" t="inlineStr">
@@ -17892,7 +18823,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G263" s="63" t="n">
+      <c r="G263" s="84" t="n">
         <v>579.95</v>
       </c>
       <c r="H263" s="47" t="inlineStr">
@@ -17941,7 +18872,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G264" s="62" t="n">
+      <c r="G264" s="83" t="n">
         <v>575.01</v>
       </c>
       <c r="H264" s="43" t="inlineStr">
@@ -17990,7 +18921,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G265" s="63" t="n">
+      <c r="G265" s="84" t="n">
         <v>572.86</v>
       </c>
       <c r="H265" s="47" t="inlineStr">
@@ -18039,7 +18970,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G266" s="62" t="n">
+      <c r="G266" s="83" t="n">
         <v>559.46</v>
       </c>
       <c r="H266" s="43" t="inlineStr">
@@ -18088,7 +19019,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G267" s="63" t="n">
+      <c r="G267" s="84" t="n">
         <v>554.74</v>
       </c>
       <c r="H267" s="47" t="inlineStr">
@@ -18137,7 +19068,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G268" s="62" t="n">
+      <c r="G268" s="83" t="n">
         <v>541.23</v>
       </c>
       <c r="H268" s="43" t="inlineStr">
@@ -18186,7 +19117,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G269" s="63" t="n">
+      <c r="G269" s="84" t="n">
         <v>528.78</v>
       </c>
       <c r="H269" s="47" t="inlineStr">
@@ -18235,7 +19166,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G270" s="62" t="n">
+      <c r="G270" s="83" t="n">
         <v>453.59</v>
       </c>
       <c r="H270" s="43" t="inlineStr">
@@ -18284,7 +19215,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G271" s="63" t="n">
+      <c r="G271" s="84" t="n">
         <v>424.39</v>
       </c>
       <c r="H271" s="47" t="inlineStr">
@@ -18334,7 +19265,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G272" s="62" t="n">
+      <c r="G272" s="83" t="n">
         <v>408.52</v>
       </c>
       <c r="H272" s="43" t="inlineStr">
@@ -18383,7 +19314,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G273" s="63" t="n">
+      <c r="G273" s="84" t="n">
         <v>389.79</v>
       </c>
       <c r="H273" s="47" t="inlineStr">
@@ -18432,7 +19363,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G274" s="62" t="n">
+      <c r="G274" s="83" t="n">
         <v>383.58</v>
       </c>
       <c r="H274" s="43" t="inlineStr">
@@ -18481,7 +19412,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G275" s="63" t="n">
+      <c r="G275" s="84" t="n">
         <v>370.9</v>
       </c>
       <c r="H275" s="47" t="inlineStr">
@@ -18530,7 +19461,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G276" s="62" t="n">
+      <c r="G276" s="83" t="n">
         <v>163.95</v>
       </c>
       <c r="H276" s="43" t="inlineStr">
@@ -18579,7 +19510,7 @@
           <t>Öne Çıkarma - Doruk Hastaneleri</t>
         </is>
       </c>
-      <c r="G277" s="63" t="n">
+      <c r="G277" s="84" t="n">
         <v>135.2</v>
       </c>
       <c r="H277" s="47" t="inlineStr">
@@ -18628,7 +19559,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G278" s="62" t="n">
+      <c r="G278" s="83" t="n">
         <v>12022.45</v>
       </c>
       <c r="H278" s="43" t="inlineStr">
@@ -18677,7 +19608,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G279" s="63" t="n">
+      <c r="G279" s="84" t="n">
         <v>11222.21</v>
       </c>
       <c r="H279" s="47" t="inlineStr">
@@ -18726,7 +19657,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G280" s="62" t="n">
+      <c r="G280" s="83" t="n">
         <v>10526.57</v>
       </c>
       <c r="H280" s="43" t="inlineStr">
@@ -18775,7 +19706,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G281" s="63" t="n">
+      <c r="G281" s="84" t="n">
         <v>9658.639999999999</v>
       </c>
       <c r="H281" s="47" t="inlineStr">
@@ -18824,7 +19755,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G282" s="62" t="n">
+      <c r="G282" s="83" t="n">
         <v>9466.969999999999</v>
       </c>
       <c r="H282" s="43" t="inlineStr">
@@ -18873,7 +19804,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G283" s="63" t="n">
+      <c r="G283" s="84" t="n">
         <v>8350.65</v>
       </c>
       <c r="H283" s="47" t="inlineStr">
@@ -18922,7 +19853,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G284" s="62" t="n">
+      <c r="G284" s="83" t="n">
         <v>8294.82</v>
       </c>
       <c r="H284" s="43" t="inlineStr">
@@ -18971,7 +19902,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G285" s="63" t="n">
+      <c r="G285" s="84" t="n">
         <v>7997.32</v>
       </c>
       <c r="H285" s="47" t="inlineStr">
@@ -19020,7 +19951,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G286" s="62" t="n">
+      <c r="G286" s="83" t="n">
         <v>7870.08</v>
       </c>
       <c r="H286" s="43" t="inlineStr">
@@ -19069,7 +20000,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G287" s="63" t="n">
+      <c r="G287" s="84" t="n">
         <v>7466.22</v>
       </c>
       <c r="H287" s="47" t="inlineStr">
@@ -19118,7 +20049,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G288" s="62" t="n">
+      <c r="G288" s="83" t="n">
         <v>7345.32</v>
       </c>
       <c r="H288" s="43" t="inlineStr">
@@ -19167,7 +20098,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G289" s="63" t="n">
+      <c r="G289" s="84" t="n">
         <v>7118.94</v>
       </c>
       <c r="H289" s="47" t="inlineStr">
@@ -19216,7 +20147,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G290" s="62" t="n">
+      <c r="G290" s="83" t="n">
         <v>7103.4</v>
       </c>
       <c r="H290" s="43" t="inlineStr">
@@ -19265,7 +20196,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G291" s="63" t="n">
+      <c r="G291" s="84" t="n">
         <v>7026.3</v>
       </c>
       <c r="H291" s="47" t="inlineStr">
@@ -19314,7 +20245,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G292" s="62" t="n">
+      <c r="G292" s="83" t="n">
         <v>6907.49</v>
       </c>
       <c r="H292" s="43" t="inlineStr">
@@ -19363,7 +20294,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G293" s="63" t="n">
+      <c r="G293" s="84" t="n">
         <v>6824.15</v>
       </c>
       <c r="H293" s="47" t="inlineStr">
@@ -19412,7 +20343,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G294" s="62" t="n">
+      <c r="G294" s="83" t="n">
         <v>6637.99</v>
       </c>
       <c r="H294" s="43" t="inlineStr">
@@ -19461,7 +20392,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G295" s="63" t="n">
+      <c r="G295" s="84" t="n">
         <v>6449.66</v>
       </c>
       <c r="H295" s="47" t="inlineStr">
@@ -19510,7 +20441,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G296" s="62" t="n">
+      <c r="G296" s="83" t="n">
         <v>6429.62</v>
       </c>
       <c r="H296" s="43" t="inlineStr">
@@ -19559,7 +20490,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G297" s="63" t="n">
+      <c r="G297" s="84" t="n">
         <v>6373.47</v>
       </c>
       <c r="H297" s="47" t="inlineStr">
@@ -19608,7 +20539,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G298" s="62" t="n">
+      <c r="G298" s="83" t="n">
         <v>6009.94</v>
       </c>
       <c r="H298" s="43" t="inlineStr">
@@ -19657,7 +20588,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G299" s="63" t="n">
+      <c r="G299" s="84" t="n">
         <v>5744.61</v>
       </c>
       <c r="H299" s="47" t="inlineStr">
@@ -19706,7 +20637,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G300" s="62" t="n">
+      <c r="G300" s="83" t="n">
         <v>5538.54</v>
       </c>
       <c r="H300" s="43" t="inlineStr">
@@ -19755,7 +20686,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G301" s="63" t="n">
+      <c r="G301" s="84" t="n">
         <v>5224.49</v>
       </c>
       <c r="H301" s="47" t="inlineStr">
@@ -19804,7 +20735,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G302" s="62" t="n">
+      <c r="G302" s="83" t="n">
         <v>4907.6</v>
       </c>
       <c r="H302" s="43" t="inlineStr">
@@ -19853,7 +20784,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G303" s="63" t="n">
+      <c r="G303" s="84" t="n">
         <v>4815.9</v>
       </c>
       <c r="H303" s="47" t="inlineStr">
@@ -19902,7 +20833,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G304" s="62" t="n">
+      <c r="G304" s="83" t="n">
         <v>4714.77</v>
       </c>
       <c r="H304" s="43" t="inlineStr">
@@ -19951,7 +20882,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G305" s="63" t="n">
+      <c r="G305" s="84" t="n">
         <v>4677.51</v>
       </c>
       <c r="H305" s="47" t="inlineStr">
@@ -20000,7 +20931,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G306" s="62" t="n">
+      <c r="G306" s="83" t="n">
         <v>4621.13</v>
       </c>
       <c r="H306" s="43" t="inlineStr">
@@ -20049,7 +20980,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G307" s="63" t="n">
+      <c r="G307" s="84" t="n">
         <v>4366.16</v>
       </c>
       <c r="H307" s="47" t="inlineStr">
@@ -20098,7 +21029,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G308" s="62" t="n">
+      <c r="G308" s="83" t="n">
         <v>4292.11</v>
       </c>
       <c r="H308" s="43" t="inlineStr">
@@ -20147,7 +21078,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G309" s="63" t="n">
+      <c r="G309" s="84" t="n">
         <v>4262.86</v>
       </c>
       <c r="H309" s="47" t="inlineStr">
@@ -20196,7 +21127,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G310" s="62" t="n">
+      <c r="G310" s="83" t="n">
         <v>4050.22</v>
       </c>
       <c r="H310" s="43" t="inlineStr">
@@ -20245,7 +21176,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G311" s="63" t="n">
+      <c r="G311" s="84" t="n">
         <v>3886.2</v>
       </c>
       <c r="H311" s="47" t="inlineStr">
@@ -20294,7 +21225,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G312" s="62" t="n">
+      <c r="G312" s="83" t="n">
         <v>3773.89</v>
       </c>
       <c r="H312" s="43" t="inlineStr">
@@ -20343,7 +21274,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G313" s="63" t="n">
+      <c r="G313" s="84" t="n">
         <v>3733.67</v>
       </c>
       <c r="H313" s="47" t="inlineStr">
@@ -20392,7 +21323,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G314" s="62" t="n">
+      <c r="G314" s="83" t="n">
         <v>3672.62</v>
       </c>
       <c r="H314" s="43" t="inlineStr">
@@ -20441,7 +21372,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G315" s="63" t="n">
+      <c r="G315" s="84" t="n">
         <v>3644.9</v>
       </c>
       <c r="H315" s="47" t="inlineStr">
@@ -20490,7 +21421,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G316" s="62" t="n">
+      <c r="G316" s="83" t="n">
         <v>3416.62</v>
       </c>
       <c r="H316" s="43" t="inlineStr">
@@ -20539,7 +21470,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G317" s="63" t="n">
+      <c r="G317" s="84" t="n">
         <v>3054.46</v>
       </c>
       <c r="H317" s="47" t="inlineStr">
@@ -20588,7 +21519,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G318" s="62" t="n">
+      <c r="G318" s="83" t="n">
         <v>2951.52</v>
       </c>
       <c r="H318" s="43" t="inlineStr">
@@ -20637,7 +21568,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G319" s="63" t="n">
+      <c r="G319" s="84" t="n">
         <v>2933.59</v>
       </c>
       <c r="H319" s="47" t="inlineStr">
@@ -20686,7 +21617,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G320" s="62" t="n">
+      <c r="G320" s="83" t="n">
         <v>2574.37</v>
       </c>
       <c r="H320" s="43" t="inlineStr">
@@ -20735,7 +21666,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G321" s="63" t="n">
+      <c r="G321" s="84" t="n">
         <v>2399.94</v>
       </c>
       <c r="H321" s="47" t="inlineStr">
@@ -20784,7 +21715,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G322" s="62" t="n">
+      <c r="G322" s="83" t="n">
         <v>2247.28</v>
       </c>
       <c r="H322" s="43" t="inlineStr">
@@ -20833,7 +21764,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G323" s="63" t="n">
+      <c r="G323" s="84" t="n">
         <v>1856.63</v>
       </c>
       <c r="H323" s="47" t="inlineStr">
@@ -20882,7 +21813,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G324" s="62" t="n">
+      <c r="G324" s="83" t="n">
         <v>1728.43</v>
       </c>
       <c r="H324" s="43" t="inlineStr">
@@ -20931,7 +21862,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G325" s="63" t="n">
+      <c r="G325" s="84" t="n">
         <v>1726.62</v>
       </c>
       <c r="H325" s="47" t="inlineStr">
@@ -20980,7 +21911,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G326" s="62" t="n">
+      <c r="G326" s="83" t="n">
         <v>1720.24</v>
       </c>
       <c r="H326" s="43" t="inlineStr">
@@ -21029,7 +21960,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G327" s="63" t="n">
+      <c r="G327" s="84" t="n">
         <v>1605.88</v>
       </c>
       <c r="H327" s="47" t="inlineStr">
@@ -21078,7 +22009,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G328" s="62" t="n">
+      <c r="G328" s="83" t="n">
         <v>1565.73</v>
       </c>
       <c r="H328" s="43" t="inlineStr">
@@ -21127,7 +22058,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G329" s="63" t="n">
+      <c r="G329" s="84" t="n">
         <v>1543.52</v>
       </c>
       <c r="H329" s="47" t="inlineStr">
@@ -21176,7 +22107,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G330" s="62" t="n">
+      <c r="G330" s="83" t="n">
         <v>1522.71</v>
       </c>
       <c r="H330" s="43" t="inlineStr">
@@ -21225,7 +22156,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G331" s="63" t="n">
+      <c r="G331" s="84" t="n">
         <v>1460.15</v>
       </c>
       <c r="H331" s="47" t="inlineStr">
@@ -21274,7 +22205,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G332" s="62" t="n">
+      <c r="G332" s="83" t="n">
         <v>1433.75</v>
       </c>
       <c r="H332" s="43" t="inlineStr">
@@ -21323,7 +22254,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G333" s="63" t="n">
+      <c r="G333" s="84" t="n">
         <v>1395.43</v>
       </c>
       <c r="H333" s="47" t="inlineStr">
@@ -21372,7 +22303,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G334" s="62" t="n">
+      <c r="G334" s="83" t="n">
         <v>1382.26</v>
       </c>
       <c r="H334" s="43" t="inlineStr">
@@ -21421,7 +22352,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G335" s="63" t="n">
+      <c r="G335" s="84" t="n">
         <v>1368.96</v>
       </c>
       <c r="H335" s="47" t="inlineStr">
@@ -21470,7 +22401,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G336" s="62" t="n">
+      <c r="G336" s="83" t="n">
         <v>1363.84</v>
       </c>
       <c r="H336" s="43" t="inlineStr">
@@ -21519,7 +22450,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G337" s="63" t="n">
+      <c r="G337" s="84" t="n">
         <v>1357.87</v>
       </c>
       <c r="H337" s="47" t="inlineStr">
@@ -21568,7 +22499,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G338" s="62" t="n">
+      <c r="G338" s="83" t="n">
         <v>1351.89</v>
       </c>
       <c r="H338" s="43" t="inlineStr">
@@ -21617,7 +22548,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G339" s="63" t="n">
+      <c r="G339" s="84" t="n">
         <v>1332.12</v>
       </c>
       <c r="H339" s="47" t="inlineStr">
@@ -21666,7 +22597,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G340" s="62" t="n">
+      <c r="G340" s="83" t="n">
         <v>1305.08</v>
       </c>
       <c r="H340" s="43" t="inlineStr">
@@ -21715,7 +22646,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G341" s="63" t="n">
+      <c r="G341" s="84" t="n">
         <v>1266.37</v>
       </c>
       <c r="H341" s="47" t="inlineStr">
@@ -21764,7 +22695,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G342" s="62" t="n">
+      <c r="G342" s="83" t="n">
         <v>1250.53</v>
       </c>
       <c r="H342" s="43" t="inlineStr">
@@ -21813,7 +22744,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G343" s="63" t="n">
+      <c r="G343" s="84" t="n">
         <v>1239.56</v>
       </c>
       <c r="H343" s="47" t="inlineStr">
@@ -21862,7 +22793,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G344" s="62" t="n">
+      <c r="G344" s="83" t="n">
         <v>1233.42</v>
       </c>
       <c r="H344" s="43" t="inlineStr">
@@ -21911,7 +22842,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G345" s="63" t="n">
+      <c r="G345" s="84" t="n">
         <v>1214.89</v>
       </c>
       <c r="H345" s="47" t="inlineStr">
@@ -21960,7 +22891,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G346" s="62" t="n">
+      <c r="G346" s="83" t="n">
         <v>1214.75</v>
       </c>
       <c r="H346" s="43" t="inlineStr">
@@ -22009,7 +22940,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G347" s="63" t="n">
+      <c r="G347" s="84" t="n">
         <v>1193.3</v>
       </c>
       <c r="H347" s="47" t="inlineStr">
@@ -22058,7 +22989,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G348" s="62" t="n">
+      <c r="G348" s="83" t="n">
         <v>1190.17</v>
       </c>
       <c r="H348" s="43" t="inlineStr"/>
@@ -22103,7 +23034,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G349" s="63" t="n">
+      <c r="G349" s="84" t="n">
         <v>1181.48</v>
       </c>
       <c r="H349" s="47" t="inlineStr">
@@ -22152,7 +23083,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G350" s="62" t="n">
+      <c r="G350" s="83" t="n">
         <v>1173.95</v>
       </c>
       <c r="H350" s="43" t="inlineStr">
@@ -22201,7 +23132,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G351" s="63" t="n">
+      <c r="G351" s="84" t="n">
         <v>1153.21</v>
       </c>
       <c r="H351" s="47" t="inlineStr">
@@ -22250,7 +23181,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G352" s="62" t="n">
+      <c r="G352" s="83" t="n">
         <v>1147.83</v>
       </c>
       <c r="H352" s="43" t="inlineStr"/>
@@ -22295,7 +23226,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G353" s="63" t="n">
+      <c r="G353" s="84" t="n">
         <v>1144.57</v>
       </c>
       <c r="H353" s="47" t="inlineStr">
@@ -22344,7 +23275,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G354" s="62" t="n">
+      <c r="G354" s="83" t="n">
         <v>1126.55</v>
       </c>
       <c r="H354" s="43" t="inlineStr">
@@ -22393,7 +23324,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G355" s="63" t="n">
+      <c r="G355" s="84" t="n">
         <v>1124.46</v>
       </c>
       <c r="H355" s="47" t="inlineStr">
@@ -22442,7 +23373,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G356" s="62" t="n">
+      <c r="G356" s="83" t="n">
         <v>1124.21</v>
       </c>
       <c r="H356" s="43" t="inlineStr">
@@ -22491,7 +23422,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G357" s="63" t="n">
+      <c r="G357" s="84" t="n">
         <v>1124.11</v>
       </c>
       <c r="H357" s="47" t="inlineStr">
@@ -22540,7 +23471,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G358" s="62" t="n">
+      <c r="G358" s="83" t="n">
         <v>1116.35</v>
       </c>
       <c r="H358" s="43" t="inlineStr">
@@ -22589,7 +23520,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G359" s="63" t="n">
+      <c r="G359" s="84" t="n">
         <v>1092.75</v>
       </c>
       <c r="H359" s="47" t="inlineStr">
@@ -22638,7 +23569,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G360" s="62" t="n">
+      <c r="G360" s="83" t="n">
         <v>1090.83</v>
       </c>
       <c r="H360" s="43" t="inlineStr">
@@ -22687,7 +23618,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G361" s="63" t="n">
+      <c r="G361" s="84" t="n">
         <v>1086.93</v>
       </c>
       <c r="H361" s="47" t="inlineStr">
@@ -22736,7 +23667,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G362" s="62" t="n">
+      <c r="G362" s="83" t="n">
         <v>1085.97</v>
       </c>
       <c r="H362" s="43" t="inlineStr">
@@ -22785,7 +23716,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G363" s="63" t="n">
+      <c r="G363" s="84" t="n">
         <v>1085.06</v>
       </c>
       <c r="H363" s="47" t="inlineStr">
@@ -22834,7 +23765,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G364" s="62" t="n">
+      <c r="G364" s="83" t="n">
         <v>1083.71</v>
       </c>
       <c r="H364" s="43" t="inlineStr">
@@ -22883,7 +23814,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G365" s="63" t="n">
+      <c r="G365" s="84" t="n">
         <v>1081.07</v>
       </c>
       <c r="H365" s="47" t="inlineStr">
@@ -22932,7 +23863,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G366" s="62" t="n">
+      <c r="G366" s="83" t="n">
         <v>1074.15</v>
       </c>
       <c r="H366" s="43" t="inlineStr">
@@ -22981,7 +23912,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G367" s="63" t="n">
+      <c r="G367" s="84" t="n">
         <v>1068.86</v>
       </c>
       <c r="H367" s="47" t="inlineStr">
@@ -23030,7 +23961,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G368" s="62" t="n">
+      <c r="G368" s="83" t="n">
         <v>1064.67</v>
       </c>
       <c r="H368" s="43" t="inlineStr"/>
@@ -23075,7 +24006,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G369" s="63" t="n">
+      <c r="G369" s="84" t="n">
         <v>1064.24</v>
       </c>
       <c r="H369" s="47" t="inlineStr">
@@ -23124,7 +24055,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G370" s="62" t="n">
+      <c r="G370" s="83" t="n">
         <v>1059.16</v>
       </c>
       <c r="H370" s="43" t="inlineStr">
@@ -23173,7 +24104,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G371" s="63" t="n">
+      <c r="G371" s="84" t="n">
         <v>1054.18</v>
       </c>
       <c r="H371" s="47" t="inlineStr"/>
@@ -23218,7 +24149,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G372" s="62" t="n">
+      <c r="G372" s="83" t="n">
         <v>1053.64</v>
       </c>
       <c r="H372" s="43" t="inlineStr">
@@ -23267,7 +24198,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G373" s="63" t="n">
+      <c r="G373" s="84" t="n">
         <v>1053.01</v>
       </c>
       <c r="H373" s="47" t="inlineStr">
@@ -23316,7 +24247,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G374" s="62" t="n">
+      <c r="G374" s="83" t="n">
         <v>1048.97</v>
       </c>
       <c r="H374" s="43" t="inlineStr">
@@ -23365,7 +24296,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G375" s="63" t="n">
+      <c r="G375" s="84" t="n">
         <v>1047.38</v>
       </c>
       <c r="H375" s="47" t="inlineStr">
@@ -23414,7 +24345,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G376" s="62" t="n">
+      <c r="G376" s="83" t="n">
         <v>1040.95</v>
       </c>
       <c r="H376" s="43" t="inlineStr">
@@ -23463,7 +24394,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G377" s="63" t="n">
+      <c r="G377" s="84" t="n">
         <v>1039.91</v>
       </c>
       <c r="H377" s="47" t="inlineStr">
@@ -23512,7 +24443,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G378" s="62" t="n">
+      <c r="G378" s="83" t="n">
         <v>1035.1</v>
       </c>
       <c r="H378" s="43" t="inlineStr">
@@ -23561,7 +24492,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G379" s="63" t="n">
+      <c r="G379" s="84" t="n">
         <v>1033.57</v>
       </c>
       <c r="H379" s="47" t="inlineStr">
@@ -23610,7 +24541,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G380" s="62" t="n">
+      <c r="G380" s="83" t="n">
         <v>1032.95</v>
       </c>
       <c r="H380" s="43" t="inlineStr">
@@ -23659,7 +24590,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G381" s="63" t="n">
+      <c r="G381" s="84" t="n">
         <v>1022.3</v>
       </c>
       <c r="H381" s="47" t="inlineStr">
@@ -23708,7 +24639,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G382" s="62" t="n">
+      <c r="G382" s="83" t="n">
         <v>1019.06</v>
       </c>
       <c r="H382" s="43" t="inlineStr">
@@ -23757,7 +24688,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G383" s="63" t="n">
+      <c r="G383" s="84" t="n">
         <v>1018.24</v>
       </c>
       <c r="H383" s="47" t="inlineStr">
@@ -23806,7 +24737,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G384" s="62" t="n">
+      <c r="G384" s="83" t="n">
         <v>1013.24</v>
       </c>
       <c r="H384" s="43" t="inlineStr">
@@ -23855,7 +24786,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G385" s="63" t="n">
+      <c r="G385" s="84" t="n">
         <v>1005.41</v>
       </c>
       <c r="H385" s="47" t="inlineStr">
@@ -23904,7 +24835,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G386" s="62" t="n">
+      <c r="G386" s="83" t="n">
         <v>1002.56</v>
       </c>
       <c r="H386" s="43" t="inlineStr">
@@ -23953,7 +24884,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G387" s="63" t="n">
+      <c r="G387" s="84" t="n">
         <v>993.74</v>
       </c>
       <c r="H387" s="47" t="inlineStr">
@@ -24002,7 +24933,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G388" s="62" t="n">
+      <c r="G388" s="83" t="n">
         <v>980.33</v>
       </c>
       <c r="H388" s="43" t="inlineStr">
@@ -24051,7 +24982,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G389" s="63" t="n">
+      <c r="G389" s="84" t="n">
         <v>980.21</v>
       </c>
       <c r="H389" s="47" t="inlineStr">
@@ -24100,7 +25031,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G390" s="62" t="n">
+      <c r="G390" s="83" t="n">
         <v>979.61</v>
       </c>
       <c r="H390" s="43" t="inlineStr">
@@ -24149,7 +25080,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G391" s="63" t="n">
+      <c r="G391" s="84" t="n">
         <v>978.8099999999999</v>
       </c>
       <c r="H391" s="47" t="inlineStr">
@@ -24198,7 +25129,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G392" s="62" t="n">
+      <c r="G392" s="83" t="n">
         <v>975.11</v>
       </c>
       <c r="H392" s="43" t="inlineStr">
@@ -24247,7 +25178,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G393" s="63" t="n">
+      <c r="G393" s="84" t="n">
         <v>973.04</v>
       </c>
       <c r="H393" s="47" t="inlineStr">
@@ -24296,7 +25227,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G394" s="62" t="n">
+      <c r="G394" s="83" t="n">
         <v>970.05</v>
       </c>
       <c r="H394" s="43" t="inlineStr"/>
@@ -24341,7 +25272,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G395" s="63" t="n">
+      <c r="G395" s="84" t="n">
         <v>969.3099999999999</v>
       </c>
       <c r="H395" s="47" t="inlineStr">
@@ -24390,7 +25321,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G396" s="62" t="n">
+      <c r="G396" s="83" t="n">
         <v>968.59</v>
       </c>
       <c r="H396" s="43" t="inlineStr">
@@ -24439,7 +25370,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G397" s="63" t="n">
+      <c r="G397" s="84" t="n">
         <v>965.02</v>
       </c>
       <c r="H397" s="47" t="inlineStr">
@@ -24488,7 +25419,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G398" s="62" t="n">
+      <c r="G398" s="83" t="n">
         <v>956.58</v>
       </c>
       <c r="H398" s="43" t="inlineStr"/>
@@ -24533,7 +25464,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G399" s="63" t="n">
+      <c r="G399" s="84" t="n">
         <v>950.42</v>
       </c>
       <c r="H399" s="47" t="inlineStr">
@@ -24582,7 +25513,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G400" s="62" t="n">
+      <c r="G400" s="83" t="n">
         <v>948.74</v>
       </c>
       <c r="H400" s="43" t="inlineStr">
@@ -24631,7 +25562,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G401" s="63" t="n">
+      <c r="G401" s="84" t="n">
         <v>939.45</v>
       </c>
       <c r="H401" s="47" t="inlineStr">
@@ -24680,7 +25611,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G402" s="62" t="n">
+      <c r="G402" s="83" t="n">
         <v>929.83</v>
       </c>
       <c r="H402" s="43" t="inlineStr">
@@ -24729,7 +25660,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G403" s="63" t="n">
+      <c r="G403" s="84" t="n">
         <v>927.3099999999999</v>
       </c>
       <c r="H403" s="47" t="inlineStr"/>
@@ -24774,7 +25705,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G404" s="62" t="n">
+      <c r="G404" s="83" t="n">
         <v>924.98</v>
       </c>
       <c r="H404" s="43" t="inlineStr">
@@ -24823,7 +25754,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G405" s="63" t="n">
+      <c r="G405" s="84" t="n">
         <v>910.99</v>
       </c>
       <c r="H405" s="47" t="inlineStr">
@@ -24872,7 +25803,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G406" s="62" t="n">
+      <c r="G406" s="83" t="n">
         <v>904.88</v>
       </c>
       <c r="H406" s="43" t="inlineStr"/>
@@ -24917,7 +25848,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G407" s="63" t="n">
+      <c r="G407" s="84" t="n">
         <v>899.37</v>
       </c>
       <c r="H407" s="47" t="inlineStr">
@@ -24966,7 +25897,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G408" s="62" t="n">
+      <c r="G408" s="83" t="n">
         <v>891.77</v>
       </c>
       <c r="H408" s="43" t="inlineStr">
@@ -25015,7 +25946,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G409" s="63" t="n">
+      <c r="G409" s="84" t="n">
         <v>883.64</v>
       </c>
       <c r="H409" s="47" t="inlineStr"/>
@@ -25060,7 +25991,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G410" s="62" t="n">
+      <c r="G410" s="83" t="n">
         <v>883.0599999999999</v>
       </c>
       <c r="H410" s="43" t="inlineStr"/>
@@ -25105,7 +26036,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G411" s="63" t="n">
+      <c r="G411" s="84" t="n">
         <v>880.75</v>
       </c>
       <c r="H411" s="47" t="inlineStr">
@@ -25154,7 +26085,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G412" s="62" t="n">
+      <c r="G412" s="83" t="n">
         <v>878.53</v>
       </c>
       <c r="H412" s="43" t="inlineStr">
@@ -25203,7 +26134,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G413" s="63" t="n">
+      <c r="G413" s="84" t="n">
         <v>876.42</v>
       </c>
       <c r="H413" s="47" t="inlineStr">
@@ -25252,7 +26183,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G414" s="62" t="n">
+      <c r="G414" s="83" t="n">
         <v>873.99</v>
       </c>
       <c r="H414" s="43" t="inlineStr">
@@ -25301,7 +26232,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G415" s="63" t="n">
+      <c r="G415" s="84" t="n">
         <v>866.54</v>
       </c>
       <c r="H415" s="47" t="inlineStr">
@@ -25350,7 +26281,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G416" s="62" t="n">
+      <c r="G416" s="83" t="n">
         <v>863.74</v>
       </c>
       <c r="H416" s="43" t="inlineStr">
@@ -25399,7 +26330,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G417" s="63" t="n">
+      <c r="G417" s="84" t="n">
         <v>863.45</v>
       </c>
       <c r="H417" s="47" t="inlineStr">
@@ -25448,7 +26379,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G418" s="62" t="n">
+      <c r="G418" s="83" t="n">
         <v>861.55</v>
       </c>
       <c r="H418" s="43" t="inlineStr">
@@ -25497,7 +26428,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G419" s="63" t="n">
+      <c r="G419" s="84" t="n">
         <v>856.3099999999999</v>
       </c>
       <c r="H419" s="47" t="inlineStr">
@@ -25546,7 +26477,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G420" s="62" t="n">
+      <c r="G420" s="83" t="n">
         <v>851.39</v>
       </c>
       <c r="H420" s="43" t="inlineStr">
@@ -25595,7 +26526,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G421" s="63" t="n">
+      <c r="G421" s="84" t="n">
         <v>831.26</v>
       </c>
       <c r="H421" s="47" t="inlineStr">
@@ -25644,7 +26575,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G422" s="62" t="n">
+      <c r="G422" s="83" t="n">
         <v>829.13</v>
       </c>
       <c r="H422" s="43" t="inlineStr"/>
@@ -25689,7 +26620,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G423" s="63" t="n">
+      <c r="G423" s="84" t="n">
         <v>821.66</v>
       </c>
       <c r="H423" s="47" t="inlineStr">
@@ -25738,7 +26669,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G424" s="62" t="n">
+      <c r="G424" s="83" t="n">
         <v>814.17</v>
       </c>
       <c r="H424" s="43" t="inlineStr">
@@ -25787,7 +26718,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G425" s="63" t="n">
+      <c r="G425" s="84" t="n">
         <v>813.54</v>
       </c>
       <c r="H425" s="47" t="inlineStr">
@@ -25836,7 +26767,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G426" s="62" t="n">
+      <c r="G426" s="83" t="n">
         <v>801.45</v>
       </c>
       <c r="H426" s="43" t="inlineStr">
@@ -25885,7 +26816,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G427" s="63" t="n">
+      <c r="G427" s="84" t="n">
         <v>793.0700000000001</v>
       </c>
       <c r="H427" s="47" t="inlineStr">
@@ -25934,7 +26865,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G428" s="62" t="n">
+      <c r="G428" s="83" t="n">
         <v>790.25</v>
       </c>
       <c r="H428" s="43" t="inlineStr">
@@ -25983,7 +26914,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G429" s="63" t="n">
+      <c r="G429" s="84" t="n">
         <v>781.66</v>
       </c>
       <c r="H429" s="47" t="inlineStr"/>
@@ -26028,7 +26959,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G430" s="62" t="n">
+      <c r="G430" s="83" t="n">
         <v>781.58</v>
       </c>
       <c r="H430" s="43" t="inlineStr"/>
@@ -26073,7 +27004,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G431" s="63" t="n">
+      <c r="G431" s="84" t="n">
         <v>757.84</v>
       </c>
       <c r="H431" s="47" t="inlineStr"/>
@@ -26118,7 +27049,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G432" s="62" t="n">
+      <c r="G432" s="83" t="n">
         <v>754.75</v>
       </c>
       <c r="H432" s="43" t="inlineStr">
@@ -26167,7 +27098,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G433" s="63" t="n">
+      <c r="G433" s="84" t="n">
         <v>754.22</v>
       </c>
       <c r="H433" s="47" t="inlineStr">
@@ -26216,7 +27147,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G434" s="62" t="n">
+      <c r="G434" s="83" t="n">
         <v>753.26</v>
       </c>
       <c r="H434" s="43" t="inlineStr">
@@ -26265,7 +27196,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G435" s="63" t="n">
+      <c r="G435" s="84" t="n">
         <v>749.17</v>
       </c>
       <c r="H435" s="47" t="inlineStr">
@@ -26314,7 +27245,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G436" s="62" t="n">
+      <c r="G436" s="83" t="n">
         <v>746.97</v>
       </c>
       <c r="H436" s="43" t="inlineStr"/>
@@ -26359,7 +27290,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G437" s="63" t="n">
+      <c r="G437" s="84" t="n">
         <v>745.54</v>
       </c>
       <c r="H437" s="47" t="inlineStr">
@@ -26408,7 +27339,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G438" s="62" t="n">
+      <c r="G438" s="83" t="n">
         <v>741.58</v>
       </c>
       <c r="H438" s="43" t="inlineStr">
@@ -26457,7 +27388,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G439" s="63" t="n">
+      <c r="G439" s="84" t="n">
         <v>732.37</v>
       </c>
       <c r="H439" s="47" t="inlineStr">
@@ -26506,7 +27437,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G440" s="62" t="n">
+      <c r="G440" s="83" t="n">
         <v>720.1900000000001</v>
       </c>
       <c r="H440" s="43" t="inlineStr"/>
@@ -26551,7 +27482,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G441" s="63" t="n">
+      <c r="G441" s="84" t="n">
         <v>717.49</v>
       </c>
       <c r="H441" s="47" t="inlineStr"/>
@@ -26596,7 +27527,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G442" s="62" t="n">
+      <c r="G442" s="83" t="n">
         <v>695.6900000000001</v>
       </c>
       <c r="H442" s="43" t="inlineStr">
@@ -26645,7 +27576,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G443" s="63" t="n">
+      <c r="G443" s="84" t="n">
         <v>688.96</v>
       </c>
       <c r="H443" s="47" t="inlineStr">
@@ -26694,7 +27625,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G444" s="62" t="n">
+      <c r="G444" s="83" t="n">
         <v>685.45</v>
       </c>
       <c r="H444" s="43" t="inlineStr">
@@ -26743,7 +27674,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G445" s="63" t="n">
+      <c r="G445" s="84" t="n">
         <v>682.26</v>
       </c>
       <c r="H445" s="47" t="inlineStr">
@@ -26792,7 +27723,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G446" s="62" t="n">
+      <c r="G446" s="83" t="n">
         <v>674.05</v>
       </c>
       <c r="H446" s="43" t="inlineStr"/>
@@ -26837,7 +27768,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G447" s="63" t="n">
+      <c r="G447" s="84" t="n">
         <v>672.74</v>
       </c>
       <c r="H447" s="47" t="inlineStr">
@@ -26886,7 +27817,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G448" s="62" t="n">
+      <c r="G448" s="83" t="n">
         <v>649.54</v>
       </c>
       <c r="H448" s="43" t="inlineStr"/>
@@ -26931,7 +27862,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G449" s="63" t="n">
+      <c r="G449" s="84" t="n">
         <v>626.7</v>
       </c>
       <c r="H449" s="47" t="inlineStr">
@@ -26980,7 +27911,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G450" s="62" t="n">
+      <c r="G450" s="83" t="n">
         <v>607.53</v>
       </c>
       <c r="H450" s="43" t="inlineStr">
@@ -27029,7 +27960,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G451" s="63" t="n">
+      <c r="G451" s="84" t="n">
         <v>605.22</v>
       </c>
       <c r="H451" s="47" t="inlineStr">
@@ -27078,7 +28009,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G452" s="62" t="n">
+      <c r="G452" s="83" t="n">
         <v>601.6799999999999</v>
       </c>
       <c r="H452" s="43" t="inlineStr">
@@ -27127,7 +28058,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G453" s="63" t="n">
+      <c r="G453" s="84" t="n">
         <v>601.35</v>
       </c>
       <c r="H453" s="47" t="inlineStr">
@@ -27176,7 +28107,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G454" s="62" t="n">
+      <c r="G454" s="83" t="n">
         <v>600.92</v>
       </c>
       <c r="H454" s="43" t="inlineStr"/>
@@ -27221,7 +28152,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G455" s="63" t="n">
+      <c r="G455" s="84" t="n">
         <v>595.79</v>
       </c>
       <c r="H455" s="47" t="inlineStr">
@@ -27270,7 +28201,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G456" s="62" t="n">
+      <c r="G456" s="83" t="n">
         <v>585.6900000000001</v>
       </c>
       <c r="H456" s="43" t="inlineStr">
@@ -27319,7 +28250,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G457" s="63" t="n">
+      <c r="G457" s="84" t="n">
         <v>578.8200000000001</v>
       </c>
       <c r="H457" s="47" t="inlineStr">
@@ -27368,7 +28299,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G458" s="62" t="n">
+      <c r="G458" s="83" t="n">
         <v>573.85</v>
       </c>
       <c r="H458" s="43" t="inlineStr">
@@ -27417,7 +28348,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G459" s="63" t="n">
+      <c r="G459" s="84" t="n">
         <v>569.76</v>
       </c>
       <c r="H459" s="47" t="inlineStr">
@@ -27466,7 +28397,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G460" s="62" t="n">
+      <c r="G460" s="83" t="n">
         <v>566.17</v>
       </c>
       <c r="H460" s="43" t="inlineStr">
@@ -27515,7 +28446,7 @@
           <t>Lead - Kadın Doğum/Gebe/FTR</t>
         </is>
       </c>
-      <c r="G461" s="63" t="n">
+      <c r="G461" s="84" t="n">
         <v>556.6900000000001</v>
       </c>
       <c r="H461" s="47" t="inlineStr">
@@ -27564,7 +28495,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G462" s="62" t="n">
+      <c r="G462" s="83" t="n">
         <v>547.72</v>
       </c>
       <c r="H462" s="43" t="inlineStr"/>
@@ -27609,7 +28540,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G463" s="63" t="n">
+      <c r="G463" s="84" t="n">
         <v>547.52</v>
       </c>
       <c r="H463" s="47" t="inlineStr"/>
@@ -27654,7 +28585,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G464" s="62" t="n">
+      <c r="G464" s="83" t="n">
         <v>544.96</v>
       </c>
       <c r="H464" s="43" t="inlineStr"/>
@@ -27699,7 +28630,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G465" s="63" t="n">
+      <c r="G465" s="84" t="n">
         <v>543.47</v>
       </c>
       <c r="H465" s="47" t="inlineStr"/>
@@ -27744,7 +28675,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G466" s="62" t="n">
+      <c r="G466" s="83" t="n">
         <v>534.36</v>
       </c>
       <c r="H466" s="43" t="inlineStr">
@@ -27793,7 +28724,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G467" s="63" t="n">
+      <c r="G467" s="84" t="n">
         <v>530.3200000000001</v>
       </c>
       <c r="H467" s="47" t="inlineStr">
@@ -27842,7 +28773,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G468" s="62" t="n">
+      <c r="G468" s="83" t="n">
         <v>524.6</v>
       </c>
       <c r="H468" s="43" t="inlineStr">
@@ -27891,7 +28822,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G469" s="63" t="n">
+      <c r="G469" s="84" t="n">
         <v>522.78</v>
       </c>
       <c r="H469" s="47" t="inlineStr"/>
@@ -27936,7 +28867,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G470" s="62" t="n">
+      <c r="G470" s="83" t="n">
         <v>522.38</v>
       </c>
       <c r="H470" s="43" t="inlineStr">
@@ -27985,7 +28916,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G471" s="63" t="n">
+      <c r="G471" s="84" t="n">
         <v>519.86</v>
       </c>
       <c r="H471" s="47" t="inlineStr"/>
@@ -28030,7 +28961,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G472" s="62" t="n">
+      <c r="G472" s="83" t="n">
         <v>517.17</v>
       </c>
       <c r="H472" s="43" t="inlineStr">
@@ -28079,7 +29010,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G473" s="63" t="n">
+      <c r="G473" s="84" t="n">
         <v>515.5</v>
       </c>
       <c r="H473" s="47" t="inlineStr">
@@ -28128,7 +29059,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G474" s="62" t="n">
+      <c r="G474" s="83" t="n">
         <v>496.3</v>
       </c>
       <c r="H474" s="43" t="inlineStr"/>
@@ -28173,7 +29104,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G475" s="63" t="n">
+      <c r="G475" s="84" t="n">
         <v>489.49</v>
       </c>
       <c r="H475" s="47" t="inlineStr">
@@ -28222,7 +29153,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G476" s="62" t="n">
+      <c r="G476" s="83" t="n">
         <v>484.5</v>
       </c>
       <c r="H476" s="43" t="inlineStr">
@@ -28271,7 +29202,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G477" s="63" t="n">
+      <c r="G477" s="84" t="n">
         <v>483.59</v>
       </c>
       <c r="H477" s="47" t="inlineStr">
@@ -28320,7 +29251,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G478" s="62" t="n">
+      <c r="G478" s="83" t="n">
         <v>481.26</v>
       </c>
       <c r="H478" s="43" t="inlineStr">
@@ -28369,7 +29300,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G479" s="63" t="n">
+      <c r="G479" s="84" t="n">
         <v>464.87</v>
       </c>
       <c r="H479" s="47" t="inlineStr">
@@ -28418,7 +29349,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G480" s="62" t="n">
+      <c r="G480" s="83" t="n">
         <v>452.09</v>
       </c>
       <c r="H480" s="43" t="inlineStr">
@@ -28467,7 +29398,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G481" s="63" t="n">
+      <c r="G481" s="84" t="n">
         <v>449.47</v>
       </c>
       <c r="H481" s="47" t="inlineStr">
@@ -28516,7 +29447,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G482" s="62" t="n">
+      <c r="G482" s="83" t="n">
         <v>445.64</v>
       </c>
       <c r="H482" s="43" t="inlineStr">
@@ -28565,7 +29496,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G483" s="63" t="n">
+      <c r="G483" s="84" t="n">
         <v>427.43</v>
       </c>
       <c r="H483" s="47" t="inlineStr">
@@ -28614,7 +29545,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G484" s="62" t="n">
+      <c r="G484" s="83" t="n">
         <v>418.93</v>
       </c>
       <c r="H484" s="43" t="inlineStr">
@@ -28663,7 +29594,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G485" s="63" t="n">
+      <c r="G485" s="84" t="n">
         <v>414.93</v>
       </c>
       <c r="H485" s="47" t="inlineStr">
@@ -28712,7 +29643,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G486" s="62" t="n">
+      <c r="G486" s="83" t="n">
         <v>414.15</v>
       </c>
       <c r="H486" s="43" t="inlineStr">
@@ -28761,7 +29692,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G487" s="63" t="n">
+      <c r="G487" s="84" t="n">
         <v>378.2</v>
       </c>
       <c r="H487" s="47" t="inlineStr"/>
@@ -28806,7 +29737,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G488" s="62" t="n">
+      <c r="G488" s="83" t="n">
         <v>376.18</v>
       </c>
       <c r="H488" s="43" t="inlineStr">
@@ -28855,7 +29786,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G489" s="63" t="n">
+      <c r="G489" s="84" t="n">
         <v>374.86</v>
       </c>
       <c r="H489" s="47" t="inlineStr">
@@ -28904,7 +29835,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G490" s="62" t="n">
+      <c r="G490" s="83" t="n">
         <v>369.9</v>
       </c>
       <c r="H490" s="43" t="inlineStr">
@@ -28953,7 +29884,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G491" s="63" t="n">
+      <c r="G491" s="84" t="n">
         <v>369.89</v>
       </c>
       <c r="H491" s="47" t="inlineStr">
@@ -29002,7 +29933,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G492" s="62" t="n">
+      <c r="G492" s="83" t="n">
         <v>368.95</v>
       </c>
       <c r="H492" s="43" t="inlineStr">
@@ -29051,7 +29982,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G493" s="63" t="n">
+      <c r="G493" s="84" t="n">
         <v>368.39</v>
       </c>
       <c r="H493" s="47" t="inlineStr"/>
@@ -29096,7 +30027,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G494" s="62" t="n">
+      <c r="G494" s="83" t="n">
         <v>366.36</v>
       </c>
       <c r="H494" s="43" t="inlineStr"/>
@@ -29141,7 +30072,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G495" s="63" t="n">
+      <c r="G495" s="84" t="n">
         <v>366.12</v>
       </c>
       <c r="H495" s="47" t="inlineStr">
@@ -29190,7 +30121,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G496" s="62" t="n">
+      <c r="G496" s="83" t="n">
         <v>365.75</v>
       </c>
       <c r="H496" s="43" t="inlineStr">
@@ -29239,7 +30170,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G497" s="63" t="n">
+      <c r="G497" s="84" t="n">
         <v>364.8</v>
       </c>
       <c r="H497" s="47" t="inlineStr"/>
@@ -29284,7 +30215,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G498" s="62" t="n">
+      <c r="G498" s="83" t="n">
         <v>364.09</v>
       </c>
       <c r="H498" s="43" t="inlineStr">
@@ -29333,7 +30264,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G499" s="63" t="n">
+      <c r="G499" s="84" t="n">
         <v>364.01</v>
       </c>
       <c r="H499" s="47" t="inlineStr">
@@ -29382,7 +30313,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G500" s="62" t="n">
+      <c r="G500" s="83" t="n">
         <v>363.47</v>
       </c>
       <c r="H500" s="43" t="inlineStr">
@@ -29431,7 +30362,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G501" s="63" t="n">
+      <c r="G501" s="84" t="n">
         <v>361.24</v>
       </c>
       <c r="H501" s="47" t="inlineStr"/>
@@ -29476,7 +30407,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G502" s="62" t="n">
+      <c r="G502" s="83" t="n">
         <v>357.8</v>
       </c>
       <c r="H502" s="43" t="inlineStr">
@@ -29525,7 +30456,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G503" s="63" t="n">
+      <c r="G503" s="84" t="n">
         <v>357.74</v>
       </c>
       <c r="H503" s="47" t="inlineStr">
@@ -29574,7 +30505,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G504" s="62" t="n">
+      <c r="G504" s="83" t="n">
         <v>355.47</v>
       </c>
       <c r="H504" s="43" t="inlineStr"/>
@@ -29619,7 +30550,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G505" s="63" t="n">
+      <c r="G505" s="84" t="n">
         <v>354.97</v>
       </c>
       <c r="H505" s="47" t="inlineStr"/>
@@ -29664,7 +30595,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G506" s="62" t="n">
+      <c r="G506" s="83" t="n">
         <v>354.09</v>
       </c>
       <c r="H506" s="43" t="inlineStr"/>
@@ -29709,7 +30640,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G507" s="63" t="n">
+      <c r="G507" s="84" t="n">
         <v>353.7</v>
       </c>
       <c r="H507" s="47" t="inlineStr">
@@ -29758,7 +30689,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G508" s="62" t="n">
+      <c r="G508" s="83" t="n">
         <v>352.58</v>
       </c>
       <c r="H508" s="43" t="inlineStr"/>
@@ -29803,7 +30734,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G509" s="63" t="n">
+      <c r="G509" s="84" t="n">
         <v>350.66</v>
       </c>
       <c r="H509" s="47" t="inlineStr">
@@ -29852,7 +30783,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G510" s="62" t="n">
+      <c r="G510" s="83" t="n">
         <v>348.35</v>
       </c>
       <c r="H510" s="43" t="inlineStr">
@@ -29901,7 +30832,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G511" s="63" t="n">
+      <c r="G511" s="84" t="n">
         <v>347.62</v>
       </c>
       <c r="H511" s="47" t="inlineStr">
@@ -29950,7 +30881,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G512" s="62" t="n">
+      <c r="G512" s="83" t="n">
         <v>346.51</v>
       </c>
       <c r="H512" s="43" t="inlineStr">
@@ -29999,7 +30930,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G513" s="63" t="n">
+      <c r="G513" s="84" t="n">
         <v>345.9</v>
       </c>
       <c r="H513" s="47" t="inlineStr">
@@ -30048,7 +30979,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G514" s="62" t="n">
+      <c r="G514" s="83" t="n">
         <v>345.48</v>
       </c>
       <c r="H514" s="43" t="inlineStr"/>
@@ -30093,7 +31024,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G515" s="63" t="n">
+      <c r="G515" s="84" t="n">
         <v>343.83</v>
       </c>
       <c r="H515" s="47" t="inlineStr">
@@ -30142,7 +31073,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G516" s="62" t="n">
+      <c r="G516" s="83" t="n">
         <v>342.71</v>
       </c>
       <c r="H516" s="43" t="inlineStr">
@@ -30191,7 +31122,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G517" s="63" t="n">
+      <c r="G517" s="84" t="n">
         <v>342.2</v>
       </c>
       <c r="H517" s="47" t="inlineStr"/>
@@ -30236,7 +31167,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G518" s="62" t="n">
+      <c r="G518" s="83" t="n">
         <v>339.64</v>
       </c>
       <c r="H518" s="43" t="inlineStr"/>
@@ -30281,7 +31212,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G519" s="63" t="n">
+      <c r="G519" s="84" t="n">
         <v>338.18</v>
       </c>
       <c r="H519" s="47" t="inlineStr">
@@ -30330,7 +31261,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G520" s="62" t="n">
+      <c r="G520" s="83" t="n">
         <v>338.12</v>
       </c>
       <c r="H520" s="43" t="inlineStr">
@@ -30379,7 +31310,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G521" s="63" t="n">
+      <c r="G521" s="84" t="n">
         <v>336.57</v>
       </c>
       <c r="H521" s="47" t="inlineStr">
@@ -30428,7 +31359,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G522" s="62" t="n">
+      <c r="G522" s="83" t="n">
         <v>336.22</v>
       </c>
       <c r="H522" s="43" t="inlineStr">
@@ -30477,7 +31408,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G523" s="63" t="n">
+      <c r="G523" s="84" t="n">
         <v>334.17</v>
       </c>
       <c r="H523" s="47" t="inlineStr">
@@ -30526,7 +31457,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G524" s="62" t="n">
+      <c r="G524" s="83" t="n">
         <v>333.44</v>
       </c>
       <c r="H524" s="43" t="inlineStr">
@@ -30575,7 +31506,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G525" s="63" t="n">
+      <c r="G525" s="84" t="n">
         <v>331.89</v>
       </c>
       <c r="H525" s="47" t="inlineStr"/>
@@ -30620,7 +31551,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G526" s="62" t="n">
+      <c r="G526" s="83" t="n">
         <v>330.91</v>
       </c>
       <c r="H526" s="43" t="inlineStr"/>
@@ -30665,7 +31596,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G527" s="63" t="n">
+      <c r="G527" s="84" t="n">
         <v>328.93</v>
       </c>
       <c r="H527" s="47" t="inlineStr">
@@ -30714,7 +31645,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G528" s="62" t="n">
+      <c r="G528" s="83" t="n">
         <v>325.91</v>
       </c>
       <c r="H528" s="43" t="inlineStr">
@@ -30763,7 +31694,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G529" s="63" t="n">
+      <c r="G529" s="84" t="n">
         <v>324.2</v>
       </c>
       <c r="H529" s="47" t="inlineStr">
@@ -30812,7 +31743,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G530" s="62" t="n">
+      <c r="G530" s="83" t="n">
         <v>323.86</v>
       </c>
       <c r="H530" s="43" t="inlineStr"/>
@@ -30857,7 +31788,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G531" s="63" t="n">
+      <c r="G531" s="84" t="n">
         <v>323.82</v>
       </c>
       <c r="H531" s="47" t="inlineStr">
@@ -30906,7 +31837,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G532" s="62" t="n">
+      <c r="G532" s="83" t="n">
         <v>322.26</v>
       </c>
       <c r="H532" s="43" t="inlineStr"/>
@@ -30951,7 +31882,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G533" s="63" t="n">
+      <c r="G533" s="84" t="n">
         <v>321.53</v>
       </c>
       <c r="H533" s="47" t="inlineStr"/>
@@ -30996,7 +31927,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G534" s="62" t="n">
+      <c r="G534" s="83" t="n">
         <v>321.23</v>
       </c>
       <c r="H534" s="43" t="inlineStr">
@@ -31045,7 +31976,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G535" s="63" t="n">
+      <c r="G535" s="84" t="n">
         <v>320.36</v>
       </c>
       <c r="H535" s="47" t="inlineStr">
@@ -31094,7 +32025,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G536" s="62" t="n">
+      <c r="G536" s="83" t="n">
         <v>320.21</v>
       </c>
       <c r="H536" s="43" t="inlineStr"/>
@@ -31139,7 +32070,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G537" s="63" t="n">
+      <c r="G537" s="84" t="n">
         <v>319.91</v>
       </c>
       <c r="H537" s="47" t="inlineStr">
@@ -31188,7 +32119,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G538" s="62" t="n">
+      <c r="G538" s="83" t="n">
         <v>319.64</v>
       </c>
       <c r="H538" s="43" t="inlineStr">
@@ -31237,7 +32168,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G539" s="63" t="n">
+      <c r="G539" s="84" t="n">
         <v>319.37</v>
       </c>
       <c r="H539" s="47" t="inlineStr">
@@ -31286,7 +32217,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G540" s="62" t="n">
+      <c r="G540" s="83" t="n">
         <v>318.56</v>
       </c>
       <c r="H540" s="43" t="inlineStr">
@@ -31335,7 +32266,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G541" s="63" t="n">
+      <c r="G541" s="84" t="n">
         <v>317.5</v>
       </c>
       <c r="H541" s="47" t="inlineStr">
@@ -31384,7 +32315,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G542" s="62" t="n">
+      <c r="G542" s="83" t="n">
         <v>317.43</v>
       </c>
       <c r="H542" s="43" t="inlineStr">
@@ -31433,7 +32364,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G543" s="63" t="n">
+      <c r="G543" s="84" t="n">
         <v>316.74</v>
       </c>
       <c r="H543" s="47" t="inlineStr">
@@ -31482,7 +32413,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G544" s="62" t="n">
+      <c r="G544" s="83" t="n">
         <v>315.28</v>
       </c>
       <c r="H544" s="43" t="inlineStr">
@@ -31531,7 +32462,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G545" s="63" t="n">
+      <c r="G545" s="84" t="n">
         <v>313.23</v>
       </c>
       <c r="H545" s="47" t="inlineStr"/>
@@ -31576,7 +32507,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G546" s="62" t="n">
+      <c r="G546" s="83" t="n">
         <v>312.71</v>
       </c>
       <c r="H546" s="43" t="inlineStr">
@@ -31625,7 +32556,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G547" s="63" t="n">
+      <c r="G547" s="84" t="n">
         <v>312.21</v>
       </c>
       <c r="H547" s="47" t="inlineStr"/>
@@ -31670,7 +32601,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G548" s="62" t="n">
+      <c r="G548" s="83" t="n">
         <v>311.62</v>
       </c>
       <c r="H548" s="43" t="inlineStr">
@@ -31719,7 +32650,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G549" s="63" t="n">
+      <c r="G549" s="84" t="n">
         <v>311.43</v>
       </c>
       <c r="H549" s="47" t="inlineStr">
@@ -31768,7 +32699,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G550" s="62" t="n">
+      <c r="G550" s="83" t="n">
         <v>309.67</v>
       </c>
       <c r="H550" s="43" t="inlineStr">
@@ -31817,7 +32748,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G551" s="63" t="n">
+      <c r="G551" s="84" t="n">
         <v>309.15</v>
       </c>
       <c r="H551" s="47" t="inlineStr">
@@ -31866,7 +32797,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G552" s="62" t="n">
+      <c r="G552" s="83" t="n">
         <v>309.15</v>
       </c>
       <c r="H552" s="43" t="inlineStr">
@@ -31915,7 +32846,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G553" s="63" t="n">
+      <c r="G553" s="84" t="n">
         <v>308.41</v>
       </c>
       <c r="H553" s="47" t="inlineStr">
@@ -31964,7 +32895,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G554" s="62" t="n">
+      <c r="G554" s="83" t="n">
         <v>308.3</v>
       </c>
       <c r="H554" s="43" t="inlineStr"/>
@@ -32009,7 +32940,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G555" s="63" t="n">
+      <c r="G555" s="84" t="n">
         <v>308.03</v>
       </c>
       <c r="H555" s="47" t="inlineStr">
@@ -32058,7 +32989,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G556" s="62" t="n">
+      <c r="G556" s="83" t="n">
         <v>307.86</v>
       </c>
       <c r="H556" s="43" t="inlineStr"/>
@@ -32103,7 +33034,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G557" s="63" t="n">
+      <c r="G557" s="84" t="n">
         <v>307.84</v>
       </c>
       <c r="H557" s="47" t="inlineStr">
@@ -32152,7 +33083,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G558" s="62" t="n">
+      <c r="G558" s="83" t="n">
         <v>304.5</v>
       </c>
       <c r="H558" s="43" t="inlineStr">
@@ -32201,7 +33132,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G559" s="63" t="n">
+      <c r="G559" s="84" t="n">
         <v>302.87</v>
       </c>
       <c r="H559" s="47" t="inlineStr">
@@ -32250,7 +33181,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G560" s="62" t="n">
+      <c r="G560" s="83" t="n">
         <v>301.99</v>
       </c>
       <c r="H560" s="43" t="inlineStr">
@@ -32299,7 +33230,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G561" s="63" t="n">
+      <c r="G561" s="84" t="n">
         <v>301.85</v>
       </c>
       <c r="H561" s="47" t="inlineStr"/>
@@ -32344,7 +33275,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G562" s="62" t="n">
+      <c r="G562" s="83" t="n">
         <v>301.07</v>
       </c>
       <c r="H562" s="43" t="inlineStr">
@@ -32393,7 +33324,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G563" s="63" t="n">
+      <c r="G563" s="84" t="n">
         <v>299.69</v>
       </c>
       <c r="H563" s="47" t="inlineStr">
@@ -32442,7 +33373,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G564" s="62" t="n">
+      <c r="G564" s="83" t="n">
         <v>297.15</v>
       </c>
       <c r="H564" s="43" t="inlineStr"/>
@@ -32487,7 +33418,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G565" s="63" t="n">
+      <c r="G565" s="84" t="n">
         <v>295.21</v>
       </c>
       <c r="H565" s="47" t="inlineStr">
@@ -32536,7 +33467,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G566" s="62" t="n">
+      <c r="G566" s="83" t="n">
         <v>293.39</v>
       </c>
       <c r="H566" s="43" t="inlineStr">
@@ -32585,7 +33516,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G567" s="63" t="n">
+      <c r="G567" s="84" t="n">
         <v>290.65</v>
       </c>
       <c r="H567" s="47" t="inlineStr">
@@ -32634,7 +33565,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G568" s="62" t="n">
+      <c r="G568" s="83" t="n">
         <v>288.46</v>
       </c>
       <c r="H568" s="43" t="inlineStr"/>
@@ -32679,7 +33610,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G569" s="63" t="n">
+      <c r="G569" s="84" t="n">
         <v>287.66</v>
       </c>
       <c r="H569" s="47" t="inlineStr">
@@ -32728,7 +33659,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G570" s="62" t="n">
+      <c r="G570" s="83" t="n">
         <v>285.43</v>
       </c>
       <c r="H570" s="43" t="inlineStr"/>
@@ -32773,7 +33704,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G571" s="63" t="n">
+      <c r="G571" s="84" t="n">
         <v>284.01</v>
       </c>
       <c r="H571" s="47" t="inlineStr"/>
@@ -32818,7 +33749,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G572" s="62" t="n">
+      <c r="G572" s="83" t="n">
         <v>281.86</v>
       </c>
       <c r="H572" s="43" t="inlineStr"/>
@@ -32863,7 +33794,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G573" s="63" t="n">
+      <c r="G573" s="84" t="n">
         <v>280.99</v>
       </c>
       <c r="H573" s="47" t="inlineStr">
@@ -32912,7 +33843,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G574" s="62" t="n">
+      <c r="G574" s="83" t="n">
         <v>279.04</v>
       </c>
       <c r="H574" s="43" t="inlineStr">
@@ -32961,7 +33892,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G575" s="63" t="n">
+      <c r="G575" s="84" t="n">
         <v>277.14</v>
       </c>
       <c r="H575" s="47" t="inlineStr"/>
@@ -33006,7 +33937,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G576" s="62" t="n">
+      <c r="G576" s="83" t="n">
         <v>277.12</v>
       </c>
       <c r="H576" s="43" t="inlineStr">
@@ -33055,7 +33986,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G577" s="63" t="n">
+      <c r="G577" s="84" t="n">
         <v>276.86</v>
       </c>
       <c r="H577" s="47" t="inlineStr"/>
@@ -33100,7 +34031,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G578" s="62" t="n">
+      <c r="G578" s="83" t="n">
         <v>276.33</v>
       </c>
       <c r="H578" s="43" t="inlineStr">
@@ -33149,7 +34080,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G579" s="63" t="n">
+      <c r="G579" s="84" t="n">
         <v>274.33</v>
       </c>
       <c r="H579" s="47" t="inlineStr">
@@ -33198,7 +34129,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G580" s="62" t="n">
+      <c r="G580" s="83" t="n">
         <v>271.95</v>
       </c>
       <c r="H580" s="43" t="inlineStr"/>
@@ -33243,7 +34174,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G581" s="63" t="n">
+      <c r="G581" s="84" t="n">
         <v>270.4</v>
       </c>
       <c r="H581" s="47" t="inlineStr"/>
@@ -33288,7 +34219,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G582" s="62" t="n">
+      <c r="G582" s="83" t="n">
         <v>270.32</v>
       </c>
       <c r="H582" s="43" t="inlineStr">
@@ -33337,7 +34268,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G583" s="63" t="n">
+      <c r="G583" s="84" t="n">
         <v>269.14</v>
       </c>
       <c r="H583" s="47" t="inlineStr">
@@ -33386,7 +34317,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G584" s="62" t="n">
+      <c r="G584" s="83" t="n">
         <v>267.77</v>
       </c>
       <c r="H584" s="43" t="inlineStr"/>
@@ -33431,7 +34362,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G585" s="63" t="n">
+      <c r="G585" s="84" t="n">
         <v>267.68</v>
       </c>
       <c r="H585" s="47" t="inlineStr"/>
@@ -33476,7 +34407,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G586" s="62" t="n">
+      <c r="G586" s="83" t="n">
         <v>265.35</v>
       </c>
       <c r="H586" s="43" t="inlineStr"/>
@@ -33521,7 +34452,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G587" s="63" t="n">
+      <c r="G587" s="84" t="n">
         <v>263.87</v>
       </c>
       <c r="H587" s="47" t="inlineStr">
@@ -33570,7 +34501,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G588" s="62" t="n">
+      <c r="G588" s="83" t="n">
         <v>262.35</v>
       </c>
       <c r="H588" s="43" t="inlineStr">
@@ -33619,7 +34550,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G589" s="63" t="n">
+      <c r="G589" s="84" t="n">
         <v>259.73</v>
       </c>
       <c r="H589" s="47" t="inlineStr"/>
@@ -33664,7 +34595,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G590" s="62" t="n">
+      <c r="G590" s="83" t="n">
         <v>258.25</v>
       </c>
       <c r="H590" s="43" t="inlineStr">
@@ -33713,7 +34644,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G591" s="63" t="n">
+      <c r="G591" s="84" t="n">
         <v>257.17</v>
       </c>
       <c r="H591" s="47" t="inlineStr"/>
@@ -33758,7 +34689,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G592" s="62" t="n">
+      <c r="G592" s="83" t="n">
         <v>254.53</v>
       </c>
       <c r="H592" s="43" t="inlineStr">
@@ -33807,7 +34738,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G593" s="63" t="n">
+      <c r="G593" s="84" t="n">
         <v>252.02</v>
       </c>
       <c r="H593" s="47" t="inlineStr">
@@ -33856,7 +34787,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G594" s="62" t="n">
+      <c r="G594" s="83" t="n">
         <v>250.4</v>
       </c>
       <c r="H594" s="43" t="inlineStr">
@@ -33905,7 +34836,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G595" s="63" t="n">
+      <c r="G595" s="84" t="n">
         <v>246.4</v>
       </c>
       <c r="H595" s="47" t="inlineStr">
@@ -33954,7 +34885,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G596" s="62" t="n">
+      <c r="G596" s="83" t="n">
         <v>246.1</v>
       </c>
       <c r="H596" s="43" t="inlineStr">
@@ -34003,7 +34934,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G597" s="63" t="n">
+      <c r="G597" s="84" t="n">
         <v>241.38</v>
       </c>
       <c r="H597" s="47" t="inlineStr"/>
@@ -34048,7 +34979,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G598" s="62" t="n">
+      <c r="G598" s="83" t="n">
         <v>240.46</v>
       </c>
       <c r="H598" s="43" t="inlineStr"/>
@@ -34093,7 +35024,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G599" s="63" t="n">
+      <c r="G599" s="84" t="n">
         <v>239.65</v>
       </c>
       <c r="H599" s="47" t="inlineStr">
@@ -34142,7 +35073,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G600" s="62" t="n">
+      <c r="G600" s="83" t="n">
         <v>239.24</v>
       </c>
       <c r="H600" s="43" t="inlineStr">
@@ -34191,7 +35122,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G601" s="63" t="n">
+      <c r="G601" s="84" t="n">
         <v>237.96</v>
       </c>
       <c r="H601" s="47" t="inlineStr">
@@ -34240,7 +35171,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G602" s="62" t="n">
+      <c r="G602" s="83" t="n">
         <v>236.68</v>
       </c>
       <c r="H602" s="43" t="inlineStr"/>
@@ -34285,7 +35216,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G603" s="63" t="n">
+      <c r="G603" s="84" t="n">
         <v>234.5</v>
       </c>
       <c r="H603" s="47" t="inlineStr"/>
@@ -34330,7 +35261,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G604" s="62" t="n">
+      <c r="G604" s="83" t="n">
         <v>233.22</v>
       </c>
       <c r="H604" s="43" t="inlineStr">
@@ -34379,7 +35310,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G605" s="63" t="n">
+      <c r="G605" s="84" t="n">
         <v>232.89</v>
       </c>
       <c r="H605" s="47" t="inlineStr">
@@ -34428,7 +35359,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G606" s="62" t="n">
+      <c r="G606" s="83" t="n">
         <v>229.64</v>
       </c>
       <c r="H606" s="43" t="inlineStr"/>
@@ -34473,7 +35404,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G607" s="63" t="n">
+      <c r="G607" s="84" t="n">
         <v>227.35</v>
       </c>
       <c r="H607" s="47" t="inlineStr"/>
@@ -34518,7 +35449,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G608" s="62" t="n">
+      <c r="G608" s="83" t="n">
         <v>226.79</v>
       </c>
       <c r="H608" s="43" t="inlineStr"/>
@@ -34563,7 +35494,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G609" s="63" t="n">
+      <c r="G609" s="84" t="n">
         <v>225.2</v>
       </c>
       <c r="H609" s="47" t="inlineStr">
@@ -34612,7 +35543,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G610" s="62" t="n">
+      <c r="G610" s="83" t="n">
         <v>219.81</v>
       </c>
       <c r="H610" s="43" t="inlineStr">
@@ -34661,7 +35592,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G611" s="63" t="n">
+      <c r="G611" s="84" t="n">
         <v>216.14</v>
       </c>
       <c r="H611" s="47" t="inlineStr">
@@ -34710,7 +35641,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G612" s="62" t="n">
+      <c r="G612" s="83" t="n">
         <v>215.8</v>
       </c>
       <c r="H612" s="43" t="inlineStr"/>
@@ -34755,7 +35686,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G613" s="63" t="n">
+      <c r="G613" s="84" t="n">
         <v>214.96</v>
       </c>
       <c r="H613" s="47" t="inlineStr"/>
@@ -34800,7 +35731,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G614" s="62" t="n">
+      <c r="G614" s="83" t="n">
         <v>209.44</v>
       </c>
       <c r="H614" s="43" t="inlineStr"/>
@@ -34845,7 +35776,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G615" s="63" t="n">
+      <c r="G615" s="84" t="n">
         <v>207.04</v>
       </c>
       <c r="H615" s="47" t="inlineStr"/>
@@ -34890,7 +35821,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G616" s="62" t="n">
+      <c r="G616" s="83" t="n">
         <v>201.99</v>
       </c>
       <c r="H616" s="43" t="inlineStr">
@@ -34939,7 +35870,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G617" s="63" t="n">
+      <c r="G617" s="84" t="n">
         <v>195.79</v>
       </c>
       <c r="H617" s="47" t="inlineStr"/>
@@ -34984,7 +35915,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G618" s="62" t="n">
+      <c r="G618" s="83" t="n">
         <v>192.38</v>
       </c>
       <c r="H618" s="43" t="inlineStr">
@@ -35033,7 +35964,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G619" s="63" t="n">
+      <c r="G619" s="84" t="n">
         <v>186.88</v>
       </c>
       <c r="H619" s="47" t="inlineStr">
@@ -35082,7 +36013,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G620" s="62" t="n">
+      <c r="G620" s="83" t="n">
         <v>186.03</v>
       </c>
       <c r="H620" s="43" t="inlineStr">
@@ -35131,7 +36062,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G621" s="63" t="n">
+      <c r="G621" s="84" t="n">
         <v>183.14</v>
       </c>
       <c r="H621" s="47" t="inlineStr">
@@ -35180,7 +36111,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G622" s="62" t="n">
+      <c r="G622" s="83" t="n">
         <v>183.04</v>
       </c>
       <c r="H622" s="43" t="inlineStr">
@@ -35229,7 +36160,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G623" s="63" t="n">
+      <c r="G623" s="84" t="n">
         <v>174.91</v>
       </c>
       <c r="H623" s="47" t="inlineStr"/>
@@ -35274,7 +36205,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G624" s="62" t="n">
+      <c r="G624" s="83" t="n">
         <v>174.23</v>
       </c>
       <c r="H624" s="43" t="inlineStr"/>
@@ -35319,7 +36250,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G625" s="63" t="n">
+      <c r="G625" s="84" t="n">
         <v>174.15</v>
       </c>
       <c r="H625" s="47" t="inlineStr"/>
@@ -35364,7 +36295,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G626" s="62" t="n">
+      <c r="G626" s="83" t="n">
         <v>169.25</v>
       </c>
       <c r="H626" s="43" t="inlineStr">
@@ -35413,7 +36344,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G627" s="63" t="n">
+      <c r="G627" s="84" t="n">
         <v>155.38</v>
       </c>
       <c r="H627" s="47" t="inlineStr"/>
@@ -35458,7 +36389,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G628" s="62" t="n">
+      <c r="G628" s="83" t="n">
         <v>155.1</v>
       </c>
       <c r="H628" s="43" t="inlineStr"/>
@@ -35503,7 +36434,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G629" s="63" t="n">
+      <c r="G629" s="84" t="n">
         <v>154.66</v>
       </c>
       <c r="H629" s="47" t="inlineStr"/>
@@ -35548,7 +36479,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G630" s="62" t="n">
+      <c r="G630" s="83" t="n">
         <v>153.31</v>
       </c>
       <c r="H630" s="43" t="inlineStr">
@@ -35597,7 +36528,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G631" s="63" t="n">
+      <c r="G631" s="84" t="n">
         <v>149.18</v>
       </c>
       <c r="H631" s="47" t="inlineStr">
@@ -35646,7 +36577,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G632" s="62" t="n">
+      <c r="G632" s="83" t="n">
         <v>149.08</v>
       </c>
       <c r="H632" s="43" t="inlineStr">
@@ -35695,7 +36626,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G633" s="63" t="n">
+      <c r="G633" s="84" t="n">
         <v>148.29</v>
       </c>
       <c r="H633" s="47" t="inlineStr"/>
@@ -35740,7 +36671,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G634" s="62" t="n">
+      <c r="G634" s="83" t="n">
         <v>147.37</v>
       </c>
       <c r="H634" s="43" t="inlineStr">
@@ -35789,7 +36720,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G635" s="63" t="n">
+      <c r="G635" s="84" t="n">
         <v>143.97</v>
       </c>
       <c r="H635" s="47" t="inlineStr"/>
@@ -35834,7 +36765,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G636" s="62" t="n">
+      <c r="G636" s="83" t="n">
         <v>143.51</v>
       </c>
       <c r="H636" s="43" t="inlineStr"/>
@@ -35879,7 +36810,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G637" s="63" t="n">
+      <c r="G637" s="84" t="n">
         <v>142.23</v>
       </c>
       <c r="H637" s="47" t="inlineStr">
@@ -35928,7 +36859,7 @@
           <t>Lead - İK/İş Başvurusu</t>
         </is>
       </c>
-      <c r="G638" s="62" t="n">
+      <c r="G638" s="83" t="n">
         <v>142.05</v>
       </c>
       <c r="H638" s="43" t="inlineStr"/>
@@ -35973,7 +36904,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G639" s="63" t="n">
+      <c r="G639" s="84" t="n">
         <v>140.77</v>
       </c>
       <c r="H639" s="47" t="inlineStr">
@@ -36022,7 +36953,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G640" s="62" t="n">
+      <c r="G640" s="83" t="n">
         <v>129.21</v>
       </c>
       <c r="H640" s="43" t="inlineStr"/>
@@ -36067,7 +36998,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G641" s="63" t="n">
+      <c r="G641" s="84" t="n">
         <v>128.98</v>
       </c>
       <c r="H641" s="47" t="inlineStr">
@@ -36116,7 +37047,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G642" s="62" t="n">
+      <c r="G642" s="83" t="n">
         <v>125.69</v>
       </c>
       <c r="H642" s="43" t="inlineStr">
@@ -36165,7 +37096,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G643" s="63" t="n">
+      <c r="G643" s="84" t="n">
         <v>99.87</v>
       </c>
       <c r="H643" s="47" t="inlineStr"/>
@@ -36210,7 +37141,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G644" s="62" t="n">
+      <c r="G644" s="83" t="n">
         <v>94.02</v>
       </c>
       <c r="H644" s="43" t="inlineStr">
@@ -36259,7 +37190,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G645" s="63" t="n">
+      <c r="G645" s="84" t="n">
         <v>91.54000000000001</v>
       </c>
       <c r="H645" s="47" t="inlineStr"/>
@@ -36304,7 +37235,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G646" s="62" t="n">
+      <c r="G646" s="83" t="n">
         <v>91.52</v>
       </c>
       <c r="H646" s="43" t="inlineStr"/>
@@ -36349,7 +37280,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G647" s="63" t="n">
+      <c r="G647" s="84" t="n">
         <v>88.64</v>
       </c>
       <c r="H647" s="47" t="inlineStr"/>
@@ -36394,7 +37325,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G648" s="62" t="n">
+      <c r="G648" s="83" t="n">
         <v>87.08</v>
       </c>
       <c r="H648" s="43" t="inlineStr">
@@ -36443,7 +37374,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G649" s="63" t="n">
+      <c r="G649" s="84" t="n">
         <v>82.01000000000001</v>
       </c>
       <c r="H649" s="47" t="inlineStr"/>
@@ -36488,7 +37419,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G650" s="62" t="n">
+      <c r="G650" s="83" t="n">
         <v>81.83</v>
       </c>
       <c r="H650" s="43" t="inlineStr">
@@ -36537,7 +37468,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G651" s="63" t="n">
+      <c r="G651" s="84" t="n">
         <v>73.8</v>
       </c>
       <c r="H651" s="47" t="inlineStr"/>
@@ -36582,7 +37513,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G652" s="62" t="n">
+      <c r="G652" s="83" t="n">
         <v>72.05</v>
       </c>
       <c r="H652" s="43" t="inlineStr">
@@ -36631,7 +37562,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G653" s="63" t="n">
+      <c r="G653" s="84" t="n">
         <v>71.5</v>
       </c>
       <c r="H653" s="47" t="inlineStr">
@@ -36680,7 +37611,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G654" s="62" t="n">
+      <c r="G654" s="83" t="n">
         <v>71.02</v>
       </c>
       <c r="H654" s="43" t="inlineStr"/>
@@ -36725,7 +37656,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G655" s="63" t="n">
+      <c r="G655" s="84" t="n">
         <v>70</v>
       </c>
       <c r="H655" s="47" t="inlineStr"/>
@@ -36770,7 +37701,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G656" s="62" t="n">
+      <c r="G656" s="83" t="n">
         <v>67.25</v>
       </c>
       <c r="H656" s="43" t="inlineStr">
@@ -36819,7 +37750,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G657" s="63" t="n">
+      <c r="G657" s="84" t="n">
         <v>63.84</v>
       </c>
       <c r="H657" s="47" t="inlineStr"/>
@@ -36864,7 +37795,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G658" s="62" t="n">
+      <c r="G658" s="83" t="n">
         <v>58.45</v>
       </c>
       <c r="H658" s="43" t="inlineStr">
@@ -36913,7 +37844,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G659" s="63" t="n">
+      <c r="G659" s="84" t="n">
         <v>57.97</v>
       </c>
       <c r="H659" s="47" t="inlineStr"/>
@@ -36958,7 +37889,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G660" s="62" t="n">
+      <c r="G660" s="83" t="n">
         <v>56.7</v>
       </c>
       <c r="H660" s="43" t="inlineStr"/>
@@ -37003,7 +37934,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G661" s="63" t="n">
+      <c r="G661" s="84" t="n">
         <v>55.85</v>
       </c>
       <c r="H661" s="47" t="inlineStr"/>
@@ -37048,7 +37979,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G662" s="62" t="n">
+      <c r="G662" s="83" t="n">
         <v>55.21</v>
       </c>
       <c r="H662" s="43" t="inlineStr"/>
@@ -37093,7 +38024,7 @@
           <t>Lead - Check-up/Tarama</t>
         </is>
       </c>
-      <c r="G663" s="63" t="n">
+      <c r="G663" s="84" t="n">
         <v>54.75</v>
       </c>
       <c r="H663" s="47" t="inlineStr"/>
@@ -37138,7 +38069,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G664" s="62" t="n">
+      <c r="G664" s="83" t="n">
         <v>53.43</v>
       </c>
       <c r="H664" s="43" t="inlineStr"/>
@@ -37183,7 +38114,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G665" s="63" t="n">
+      <c r="G665" s="84" t="n">
         <v>47.7</v>
       </c>
       <c r="H665" s="47" t="inlineStr"/>
@@ -37228,7 +38159,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G666" s="62" t="n">
+      <c r="G666" s="83" t="n">
         <v>45.42</v>
       </c>
       <c r="H666" s="43" t="inlineStr"/>
@@ -37273,7 +38204,7 @@
           <t>Lead - Estetik/Plastik/Saç</t>
         </is>
       </c>
-      <c r="G667" s="63" t="n">
+      <c r="G667" s="84" t="n">
         <v>42.7</v>
       </c>
       <c r="H667" s="47" t="inlineStr"/>
@@ -37318,7 +38249,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G668" s="62" t="n">
+      <c r="G668" s="83" t="n">
         <v>9323.719999999999</v>
       </c>
       <c r="H668" s="43" t="inlineStr">
@@ -37367,7 +38298,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G669" s="63" t="n">
+      <c r="G669" s="84" t="n">
         <v>9066.52</v>
       </c>
       <c r="H669" s="47" t="inlineStr">
@@ -37416,7 +38347,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G670" s="62" t="n">
+      <c r="G670" s="83" t="n">
         <v>9012.73</v>
       </c>
       <c r="H670" s="43" t="inlineStr">
@@ -37465,7 +38396,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G671" s="63" t="n">
+      <c r="G671" s="84" t="n">
         <v>8745.52</v>
       </c>
       <c r="H671" s="47" t="inlineStr">
@@ -37514,7 +38445,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G672" s="62" t="n">
+      <c r="G672" s="83" t="n">
         <v>7625.57</v>
       </c>
       <c r="H672" s="43" t="inlineStr">
@@ -37563,7 +38494,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G673" s="63" t="n">
+      <c r="G673" s="84" t="n">
         <v>7564.69</v>
       </c>
       <c r="H673" s="47" t="inlineStr">
@@ -37612,7 +38543,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G674" s="62" t="n">
+      <c r="G674" s="83" t="n">
         <v>6637.97</v>
       </c>
       <c r="H674" s="43" t="inlineStr">
@@ -37661,7 +38592,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G675" s="63" t="n">
+      <c r="G675" s="84" t="n">
         <v>6523.32</v>
       </c>
       <c r="H675" s="47" t="inlineStr">
@@ -37710,7 +38641,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G676" s="62" t="n">
+      <c r="G676" s="83" t="n">
         <v>6503.7</v>
       </c>
       <c r="H676" s="43" t="inlineStr">
@@ -37759,7 +38690,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G677" s="63" t="n">
+      <c r="G677" s="84" t="n">
         <v>5888.94</v>
       </c>
       <c r="H677" s="47" t="inlineStr">
@@ -37808,7 +38739,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G678" s="62" t="n">
+      <c r="G678" s="83" t="n">
         <v>5429.68</v>
       </c>
       <c r="H678" s="43" t="inlineStr">
@@ -37857,7 +38788,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G679" s="63" t="n">
+      <c r="G679" s="84" t="n">
         <v>5210.7</v>
       </c>
       <c r="H679" s="47" t="inlineStr">
@@ -37906,7 +38837,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G680" s="62" t="n">
+      <c r="G680" s="83" t="n">
         <v>5186.35</v>
       </c>
       <c r="H680" s="43" t="inlineStr">
@@ -37955,7 +38886,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G681" s="63" t="n">
+      <c r="G681" s="84" t="n">
         <v>5036.82</v>
       </c>
       <c r="H681" s="47" t="inlineStr">
@@ -38004,7 +38935,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G682" s="62" t="n">
+      <c r="G682" s="83" t="n">
         <v>4955.58</v>
       </c>
       <c r="H682" s="43" t="inlineStr">
@@ -38053,7 +38984,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G683" s="63" t="n">
+      <c r="G683" s="84" t="n">
         <v>4786.77</v>
       </c>
       <c r="H683" s="47" t="inlineStr">
@@ -38102,7 +39033,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G684" s="62" t="n">
+      <c r="G684" s="83" t="n">
         <v>4769.89</v>
       </c>
       <c r="H684" s="43" t="inlineStr">
@@ -38151,7 +39082,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G685" s="63" t="n">
+      <c r="G685" s="84" t="n">
         <v>4285.7</v>
       </c>
       <c r="H685" s="47" t="inlineStr">
@@ -38200,7 +39131,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G686" s="62" t="n">
+      <c r="G686" s="83" t="n">
         <v>4021.96</v>
       </c>
       <c r="H686" s="43" t="inlineStr">
@@ -38249,7 +39180,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G687" s="63" t="n">
+      <c r="G687" s="84" t="n">
         <v>3792.25</v>
       </c>
       <c r="H687" s="47" t="inlineStr">
@@ -38298,7 +39229,7 @@
           <t>Bilinirlik - Kurumsal (ÖSS-TSS)</t>
         </is>
       </c>
-      <c r="G688" s="62" t="n">
+      <c r="G688" s="83" t="n">
         <v>3446.44</v>
       </c>
       <c r="H688" s="43" t="inlineStr">
@@ -38347,7 +39278,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G689" s="63" t="n">
+      <c r="G689" s="84" t="n">
         <v>3356.44</v>
       </c>
       <c r="H689" s="47" t="inlineStr">
@@ -38396,7 +39327,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G690" s="62" t="n">
+      <c r="G690" s="83" t="n">
         <v>3188.6</v>
       </c>
       <c r="H690" s="43" t="inlineStr">
@@ -38445,7 +39376,7 @@
           <t>Bilinirlik - Kurumsal (ÖSS-TSS)</t>
         </is>
       </c>
-      <c r="G691" s="63" t="n">
+      <c r="G691" s="84" t="n">
         <v>3107.89</v>
       </c>
       <c r="H691" s="47" t="inlineStr">
@@ -38494,7 +39425,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G692" s="62" t="n">
+      <c r="G692" s="83" t="n">
         <v>2797.49</v>
       </c>
       <c r="H692" s="43" t="inlineStr">
@@ -38543,7 +39474,7 @@
           <t>Bilinirlik - Kurumsal (ÖSS-TSS)</t>
         </is>
       </c>
-      <c r="G693" s="63" t="n">
+      <c r="G693" s="84" t="n">
         <v>2775.26</v>
       </c>
       <c r="H693" s="47" t="inlineStr">
@@ -38592,7 +39523,7 @@
           <t>Bilinirlik - Kurumsal (ÖSS-TSS)</t>
         </is>
       </c>
-      <c r="G694" s="62" t="n">
+      <c r="G694" s="83" t="n">
         <v>2655.96</v>
       </c>
       <c r="H694" s="43" t="inlineStr">
@@ -38641,7 +39572,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G695" s="63" t="n">
+      <c r="G695" s="84" t="n">
         <v>2605.82</v>
       </c>
       <c r="H695" s="47" t="inlineStr">
@@ -38690,7 +39621,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G696" s="62" t="n">
+      <c r="G696" s="83" t="n">
         <v>2497.92</v>
       </c>
       <c r="H696" s="43" t="inlineStr">
@@ -38739,7 +39670,7 @@
           <t>Bilinirlik - Kurumsal (ÖSS-TSS)</t>
         </is>
       </c>
-      <c r="G697" s="63" t="n">
+      <c r="G697" s="84" t="n">
         <v>2391.07</v>
       </c>
       <c r="H697" s="47" t="inlineStr">
@@ -38788,7 +39719,7 @@
           <t>Bilinirlik - Kurumsal (ÖSS-TSS)</t>
         </is>
       </c>
-      <c r="G698" s="62" t="n">
+      <c r="G698" s="83" t="n">
         <v>2328.17</v>
       </c>
       <c r="H698" s="43" t="inlineStr">
@@ -38837,7 +39768,7 @@
           <t>Bilinirlik - Kurumsal (ÖSS-TSS)</t>
         </is>
       </c>
-      <c r="G699" s="63" t="n">
+      <c r="G699" s="84" t="n">
         <v>2269.08</v>
       </c>
       <c r="H699" s="47" t="inlineStr">
@@ -38886,7 +39817,7 @@
           <t>Bilinirlik - Kurumsal (ÖSS-TSS)</t>
         </is>
       </c>
-      <c r="G700" s="62" t="n">
+      <c r="G700" s="83" t="n">
         <v>2242.3</v>
       </c>
       <c r="H700" s="43" t="inlineStr">
@@ -38935,7 +39866,7 @@
           <t>Bilinirlik - Kurumsal (ÖSS-TSS)</t>
         </is>
       </c>
-      <c r="G701" s="63" t="n">
+      <c r="G701" s="84" t="n">
         <v>2241.4</v>
       </c>
       <c r="H701" s="47" t="inlineStr">
@@ -38984,7 +39915,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G702" s="62" t="n">
+      <c r="G702" s="83" t="n">
         <v>2137.07</v>
       </c>
       <c r="H702" s="43" t="inlineStr">
@@ -39033,7 +39964,7 @@
           <t>Bilinirlik - Kurumsal (ÖSS-TSS)</t>
         </is>
       </c>
-      <c r="G703" s="63" t="n">
+      <c r="G703" s="84" t="n">
         <v>2011.91</v>
       </c>
       <c r="H703" s="47" t="inlineStr">
@@ -39082,7 +40013,7 @@
           <t>Bilinirlik - Kurumsal (ÖSS-TSS)</t>
         </is>
       </c>
-      <c r="G704" s="62" t="n">
+      <c r="G704" s="83" t="n">
         <v>1968.09</v>
       </c>
       <c r="H704" s="43" t="inlineStr">
@@ -39131,7 +40062,7 @@
           <t>Bilinirlik - Kurumsal (ÖSS-TSS)</t>
         </is>
       </c>
-      <c r="G705" s="63" t="n">
+      <c r="G705" s="84" t="n">
         <v>1908.43</v>
       </c>
       <c r="H705" s="47" t="inlineStr">
@@ -39180,7 +40111,7 @@
           <t>Bilinirlik - Kurumsal (ÖSS-TSS)</t>
         </is>
       </c>
-      <c r="G706" s="62" t="n">
+      <c r="G706" s="83" t="n">
         <v>1897.98</v>
       </c>
       <c r="H706" s="43" t="inlineStr">
@@ -39229,7 +40160,7 @@
           <t>Bilinirlik - Kurumsal (ÖSS-TSS)</t>
         </is>
       </c>
-      <c r="G707" s="63" t="n">
+      <c r="G707" s="84" t="n">
         <v>1871.14</v>
       </c>
       <c r="H707" s="47" t="inlineStr">
@@ -39278,7 +40209,7 @@
           <t>Bilinirlik - Kurumsal (ÖSS-TSS)</t>
         </is>
       </c>
-      <c r="G708" s="62" t="n">
+      <c r="G708" s="83" t="n">
         <v>1801.4</v>
       </c>
       <c r="H708" s="43" t="inlineStr">
@@ -39327,7 +40258,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G709" s="63" t="n">
+      <c r="G709" s="84" t="n">
         <v>1722.42</v>
       </c>
       <c r="H709" s="47" t="inlineStr">
@@ -39376,7 +40307,7 @@
           <t>Bilinirlik - Gebe/Doğum</t>
         </is>
       </c>
-      <c r="G710" s="62" t="n">
+      <c r="G710" s="83" t="n">
         <v>1716.48</v>
       </c>
       <c r="H710" s="43" t="inlineStr">
@@ -39425,7 +40356,7 @@
           <t>Bilinirlik - Kurumsal (ÖSS-TSS)</t>
         </is>
       </c>
-      <c r="G711" s="63" t="n">
+      <c r="G711" s="84" t="n">
         <v>1622.9</v>
       </c>
       <c r="H711" s="47" t="inlineStr">
@@ -39474,7 +40405,7 @@
           <t>Bilinirlik - Gebe/Doğum</t>
         </is>
       </c>
-      <c r="G712" s="62" t="n">
+      <c r="G712" s="83" t="n">
         <v>1563.95</v>
       </c>
       <c r="H712" s="43" t="inlineStr">
@@ -39523,7 +40454,7 @@
           <t>Bilinirlik - Kurumsal (ÖSS-TSS)</t>
         </is>
       </c>
-      <c r="G713" s="63" t="n">
+      <c r="G713" s="84" t="n">
         <v>1559.24</v>
       </c>
       <c r="H713" s="47" t="inlineStr">
@@ -39572,7 +40503,7 @@
           <t>Bilinirlik - Kurumsal (ÖSS-TSS)</t>
         </is>
       </c>
-      <c r="G714" s="62" t="n">
+      <c r="G714" s="83" t="n">
         <v>1503.68</v>
       </c>
       <c r="H714" s="43" t="inlineStr">
@@ -39621,7 +40552,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G715" s="63" t="n">
+      <c r="G715" s="84" t="n">
         <v>1494.73</v>
       </c>
       <c r="H715" s="47" t="inlineStr">
@@ -39670,7 +40601,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G716" s="62" t="n">
+      <c r="G716" s="83" t="n">
         <v>1414.73</v>
       </c>
       <c r="H716" s="43" t="inlineStr">
@@ -39719,7 +40650,7 @@
           <t>Bilinirlik - Gebe/Doğum</t>
         </is>
       </c>
-      <c r="G717" s="63" t="n">
+      <c r="G717" s="84" t="n">
         <v>1411.28</v>
       </c>
       <c r="H717" s="47" t="inlineStr">
@@ -39768,7 +40699,7 @@
           <t>Bilinirlik - Gebe/Doğum</t>
         </is>
       </c>
-      <c r="G718" s="62" t="n">
+      <c r="G718" s="83" t="n">
         <v>1408.87</v>
       </c>
       <c r="H718" s="43" t="inlineStr">
@@ -39817,7 +40748,7 @@
           <t>Bilinirlik - Gebe/Doğum</t>
         </is>
       </c>
-      <c r="G719" s="63" t="n">
+      <c r="G719" s="84" t="n">
         <v>1398.59</v>
       </c>
       <c r="H719" s="47" t="inlineStr">
@@ -39866,7 +40797,7 @@
           <t>Bilinirlik - Kurumsal (ÖSS-TSS)</t>
         </is>
       </c>
-      <c r="G720" s="62" t="n">
+      <c r="G720" s="83" t="n">
         <v>1333.5</v>
       </c>
       <c r="H720" s="43" t="inlineStr">
@@ -39915,7 +40846,7 @@
           <t>Bilinirlik - Gebe/Doğum</t>
         </is>
       </c>
-      <c r="G721" s="63" t="n">
+      <c r="G721" s="84" t="n">
         <v>1280.72</v>
       </c>
       <c r="H721" s="47" t="inlineStr">
@@ -39964,7 +40895,7 @@
           <t>Bilinirlik - Kurumsal (ÖSS-TSS)</t>
         </is>
       </c>
-      <c r="G722" s="62" t="n">
+      <c r="G722" s="83" t="n">
         <v>1252.95</v>
       </c>
       <c r="H722" s="43" t="inlineStr">
@@ -40013,7 +40944,7 @@
           <t>Bilinirlik - Kurumsal (ÖSS-TSS)</t>
         </is>
       </c>
-      <c r="G723" s="63" t="n">
+      <c r="G723" s="84" t="n">
         <v>1197.21</v>
       </c>
       <c r="H723" s="47" t="inlineStr">
@@ -40062,7 +40993,7 @@
           <t>Bilinirlik - Gebe/Doğum</t>
         </is>
       </c>
-      <c r="G724" s="62" t="n">
+      <c r="G724" s="83" t="n">
         <v>1179.06</v>
       </c>
       <c r="H724" s="43" t="inlineStr">
@@ -40111,7 +41042,7 @@
           <t>Bilinirlik - Gebe/Doğum</t>
         </is>
       </c>
-      <c r="G725" s="63" t="n">
+      <c r="G725" s="84" t="n">
         <v>1065.31</v>
       </c>
       <c r="H725" s="47" t="inlineStr">
@@ -40160,7 +41091,7 @@
           <t>Bilinirlik - Gebe/Doğum</t>
         </is>
       </c>
-      <c r="G726" s="62" t="n">
+      <c r="G726" s="83" t="n">
         <v>1052.72</v>
       </c>
       <c r="H726" s="43" t="inlineStr">
@@ -40209,7 +41140,7 @@
           <t>Bilinirlik - Gebe/Doğum</t>
         </is>
       </c>
-      <c r="G727" s="63" t="n">
+      <c r="G727" s="84" t="n">
         <v>1027.51</v>
       </c>
       <c r="H727" s="47" t="inlineStr">
@@ -40258,7 +41189,7 @@
           <t>Bilinirlik - Gebe/Doğum</t>
         </is>
       </c>
-      <c r="G728" s="62" t="n">
+      <c r="G728" s="83" t="n">
         <v>1024.33</v>
       </c>
       <c r="H728" s="43" t="inlineStr">
@@ -40307,7 +41238,7 @@
           <t>Bilinirlik - Gebe/Doğum</t>
         </is>
       </c>
-      <c r="G729" s="63" t="n">
+      <c r="G729" s="84" t="n">
         <v>1019.36</v>
       </c>
       <c r="H729" s="47" t="inlineStr">
@@ -40356,7 +41287,7 @@
           <t>Bilinirlik - Kurumsal (ÖSS-TSS)</t>
         </is>
       </c>
-      <c r="G730" s="62" t="n">
+      <c r="G730" s="83" t="n">
         <v>1015.44</v>
       </c>
       <c r="H730" s="43" t="inlineStr">
@@ -40405,7 +41336,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G731" s="63" t="n">
+      <c r="G731" s="84" t="n">
         <v>1004.04</v>
       </c>
       <c r="H731" s="47" t="inlineStr">
@@ -40454,7 +41385,7 @@
           <t>Bilinirlik - Gebe/Doğum</t>
         </is>
       </c>
-      <c r="G732" s="62" t="n">
+      <c r="G732" s="83" t="n">
         <v>991.9299999999999</v>
       </c>
       <c r="H732" s="43" t="inlineStr">
@@ -40503,7 +41434,7 @@
           <t>Bilinirlik - Gebe/Doğum</t>
         </is>
       </c>
-      <c r="G733" s="63" t="n">
+      <c r="G733" s="84" t="n">
         <v>964.29</v>
       </c>
       <c r="H733" s="47" t="inlineStr">
@@ -40552,7 +41483,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G734" s="62" t="n">
+      <c r="G734" s="83" t="n">
         <v>934.55</v>
       </c>
       <c r="H734" s="43" t="inlineStr">
@@ -40601,7 +41532,7 @@
           <t>Bilinirlik - Gebe/Doğum</t>
         </is>
       </c>
-      <c r="G735" s="63" t="n">
+      <c r="G735" s="84" t="n">
         <v>882.4400000000001</v>
       </c>
       <c r="H735" s="47" t="inlineStr">
@@ -40650,7 +41581,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G736" s="62" t="n">
+      <c r="G736" s="83" t="n">
         <v>824.79</v>
       </c>
       <c r="H736" s="43" t="inlineStr">
@@ -40699,7 +41630,7 @@
           <t>Bilinirlik - Gebe/Doğum</t>
         </is>
       </c>
-      <c r="G737" s="63" t="n">
+      <c r="G737" s="84" t="n">
         <v>812.9299999999999</v>
       </c>
       <c r="H737" s="47" t="inlineStr">
@@ -40748,7 +41679,7 @@
           <t>Bilinirlik - Gebe/Doğum</t>
         </is>
       </c>
-      <c r="G738" s="62" t="n">
+      <c r="G738" s="83" t="n">
         <v>776.67</v>
       </c>
       <c r="H738" s="43" t="inlineStr">
@@ -40797,7 +41728,7 @@
           <t>Bilinirlik - Gebe/Doğum</t>
         </is>
       </c>
-      <c r="G739" s="63" t="n">
+      <c r="G739" s="84" t="n">
         <v>725.66</v>
       </c>
       <c r="H739" s="47" t="inlineStr">
@@ -40846,7 +41777,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G740" s="62" t="n">
+      <c r="G740" s="83" t="n">
         <v>663.13</v>
       </c>
       <c r="H740" s="43" t="inlineStr">
@@ -40895,7 +41826,7 @@
           <t>Bilinirlik - Gebe/Doğum</t>
         </is>
       </c>
-      <c r="G741" s="63" t="n">
+      <c r="G741" s="84" t="n">
         <v>661.38</v>
       </c>
       <c r="H741" s="47" t="inlineStr">
@@ -40944,7 +41875,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G742" s="62" t="n">
+      <c r="G742" s="83" t="n">
         <v>627.58</v>
       </c>
       <c r="H742" s="43" t="inlineStr">
@@ -40993,7 +41924,7 @@
           <t>Bilinirlik - Gebe/Doğum</t>
         </is>
       </c>
-      <c r="G743" s="63" t="n">
+      <c r="G743" s="84" t="n">
         <v>626</v>
       </c>
       <c r="H743" s="47" t="inlineStr">
@@ -41042,7 +41973,7 @@
           <t>Bilinirlik - Gebe/Doğum</t>
         </is>
       </c>
-      <c r="G744" s="62" t="n">
+      <c r="G744" s="83" t="n">
         <v>615.6799999999999</v>
       </c>
       <c r="H744" s="43" t="inlineStr">
@@ -41091,7 +42022,7 @@
           <t>Bilinirlik - Kurumsal (ÖSS-TSS)</t>
         </is>
       </c>
-      <c r="G745" s="63" t="n">
+      <c r="G745" s="84" t="n">
         <v>490.19</v>
       </c>
       <c r="H745" s="47" t="inlineStr">
@@ -41140,7 +42071,7 @@
           <t>Bilinirlik - Gebe/Doğum</t>
         </is>
       </c>
-      <c r="G746" s="62" t="n">
+      <c r="G746" s="83" t="n">
         <v>444.94</v>
       </c>
       <c r="H746" s="43" t="inlineStr">
@@ -41189,7 +42120,7 @@
           <t>Bilinirlik - Kurumsal (ÖSS-TSS)</t>
         </is>
       </c>
-      <c r="G747" s="63" t="n">
+      <c r="G747" s="84" t="n">
         <v>432.96</v>
       </c>
       <c r="H747" s="47" t="inlineStr">
@@ -41238,7 +42169,7 @@
           <t>Bilinirlik - Kurumsal (ÖSS-TSS)</t>
         </is>
       </c>
-      <c r="G748" s="62" t="n">
+      <c r="G748" s="83" t="n">
         <v>430.39</v>
       </c>
       <c r="H748" s="43" t="inlineStr">
@@ -41287,7 +42218,7 @@
           <t>Bilinirlik - Kurumsal (ÖSS-TSS)</t>
         </is>
       </c>
-      <c r="G749" s="63" t="n">
+      <c r="G749" s="84" t="n">
         <v>408.31</v>
       </c>
       <c r="H749" s="47" t="inlineStr">
@@ -41336,7 +42267,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G750" s="62" t="n">
+      <c r="G750" s="83" t="n">
         <v>382.36</v>
       </c>
       <c r="H750" s="43" t="inlineStr">
@@ -41385,7 +42316,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G751" s="63" t="n">
+      <c r="G751" s="84" t="n">
         <v>285.05</v>
       </c>
       <c r="H751" s="47" t="inlineStr">
@@ -41434,7 +42365,7 @@
           <t>Bilinirlik - Gebe/Doğum</t>
         </is>
       </c>
-      <c r="G752" s="62" t="n">
+      <c r="G752" s="83" t="n">
         <v>243.23</v>
       </c>
       <c r="H752" s="43" t="inlineStr">
@@ -41483,7 +42414,7 @@
           <t>Bilinirlik - Gebe/Doğum</t>
         </is>
       </c>
-      <c r="G753" s="63" t="n">
+      <c r="G753" s="84" t="n">
         <v>234.53</v>
       </c>
       <c r="H753" s="47" t="inlineStr">
@@ -41532,7 +42463,7 @@
           <t>Bilinirlik - Gebe/Doğum</t>
         </is>
       </c>
-      <c r="G754" s="62" t="n">
+      <c r="G754" s="83" t="n">
         <v>219.15</v>
       </c>
       <c r="H754" s="43" t="inlineStr">
@@ -41581,7 +42512,7 @@
           <t>Bilinirlik - Gebe/Doğum</t>
         </is>
       </c>
-      <c r="G755" s="63" t="n">
+      <c r="G755" s="84" t="n">
         <v>142.81</v>
       </c>
       <c r="H755" s="47" t="inlineStr">
@@ -41630,7 +42561,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G756" s="62" t="n">
+      <c r="G756" s="83" t="n">
         <v>124.1</v>
       </c>
       <c r="H756" s="43" t="inlineStr">
@@ -41679,7 +42610,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G757" s="63" t="n">
+      <c r="G757" s="84" t="n">
         <v>93.72</v>
       </c>
       <c r="H757" s="47" t="inlineStr">
@@ -41728,7 +42659,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G758" s="62" t="n">
+      <c r="G758" s="83" t="n">
         <v>92.98999999999999</v>
       </c>
       <c r="H758" s="43" t="inlineStr">
@@ -41777,7 +42708,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G759" s="63" t="n">
+      <c r="G759" s="84" t="n">
         <v>91.3</v>
       </c>
       <c r="H759" s="47" t="inlineStr">
@@ -41826,7 +42757,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G760" s="62" t="n">
+      <c r="G760" s="83" t="n">
         <v>67.40000000000001</v>
       </c>
       <c r="H760" s="43" t="inlineStr">
@@ -41875,7 +42806,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G761" s="63" t="n">
+      <c r="G761" s="84" t="n">
         <v>64.45999999999999</v>
       </c>
       <c r="H761" s="47" t="inlineStr">
@@ -41924,7 +42855,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G762" s="62" t="n">
+      <c r="G762" s="83" t="n">
         <v>46.51</v>
       </c>
       <c r="H762" s="43" t="inlineStr">
@@ -41973,7 +42904,7 @@
           <t>Bilinirlik - Doktor Tanıtım</t>
         </is>
       </c>
-      <c r="G763" s="63" t="n">
+      <c r="G763" s="84" t="n">
         <v>23.13</v>
       </c>
       <c r="H763" s="47" t="inlineStr">
